--- a/oracle/dist/20261027_Oracle個股模型_v0.4.xlsx
+++ b/oracle/dist/20261027_Oracle個股模型_v0.4.xlsx
@@ -276,7 +276,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2333" uniqueCount="1018">
   <si>
     <r>
       <rPr>
@@ -12664,7 +12664,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">在役設備</t>
+      <t xml:space="preserve">在役設備；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起隨非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收等比例</t>
     </r>
   </si>
   <si>
@@ -13041,7 +13079,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">折舊設為等於非 </t>
+      <t xml:space="preserve">折舊另以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2024 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">水準隨非 </t>
     </r>
     <r>
       <rPr>
@@ -13060,7 +13117,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">資本支出（穩態）</t>
+      <t xml:space="preserve">營收等比例（不隨本參數變動）</t>
     </r>
   </si>
   <si>
@@ -27715,7 +27772,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">折舊（＝非 </t>
+      <t xml:space="preserve">折舊（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2024 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">水準每季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.782</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，隨非 </t>
     </r>
     <r>
       <rPr>
@@ -27734,7 +27829,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">資本支出，穩態）＋無形資產攤銷</t>
+      <t xml:space="preserve">營收相對 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">等比例）＋無形資產攤銷</t>
     </r>
   </si>
   <si>
@@ -36362,26 +36476,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">未重算（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">data/sens_v04.json </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不存在）</t>
+      <t xml:space="preserve">重算日期 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；基準加權目標價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">133.2323</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（應等於 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁加權目標價，見下方檢查列）</t>
     </r>
   </si>
   <si>
@@ -36561,6 +36713,1228 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">定價倍數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k ×0.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×1.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">約當 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Oracle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自身合約）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">計費比例</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">併網速度（三情境）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×0.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×1.2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">合約容量上限（三情境）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×0.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×1.1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">建設延誤（三情境）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全部 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月／各加 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">折舊年限</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營運費用</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">未起租租約期限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OCI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">其他（非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年增</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SaaS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">長期年增</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Software support </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">長期年增</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">−3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OCI AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以外」利潤率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">m_sw</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">−3pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+3pt</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">未分攤費用年增</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">客戶出資覆蓋比</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22.2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">37%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Beta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WACC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">永續成長率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">g</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分部倍數（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OCI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與其餘業務）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">權重</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資本支出 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資本支出（指引）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">95</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">檢查：重算基準加權目標價 − </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁加權目標價（應為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">說明：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tornado </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以「低：相對基準」「高：相對基準」兩欄；情境結構（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）不變，只動一個輸入。容量情境本身的差異見 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁情境目標價</t>
     </r>
   </si>
   <si>
@@ -37824,7 +39198,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -37835,6 +39209,7 @@
     <numFmt numFmtId="171" formatCode="#,##0.0"/>
     <numFmt numFmtId="172" formatCode="0.00%"/>
     <numFmt numFmtId="173" formatCode="@"/>
+    <numFmt numFmtId="174" formatCode="0.0000"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -37964,7 +39339,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -38086,6 +39461,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="173" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -38365,7 +39752,7 @@
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="str">
         <f aca="false">"投資建議："&amp;Val!C67&amp;"（加權目標價 US$"&amp;TEXT(Val!C61,"0.0")&amp;"，現價 US$"&amp;TEXT(px,"0.00")&amp;"〔2026-10-26〕，上檔空間 "&amp;TEXT(Val!C64,"+0.0%;-0.0%")&amp;"）"</f>
-        <v>投資建議：中立（加權目標價 US$141.2，現價 US$126.06〔2026-10-26〕，上檔空間 +12.0%）</v>
+        <v>投資建議：中立（加權目標價 US$133.2，現價 US$126.06〔2026-10-26〕，上檔空間 +5.7%）</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38377,13 +39764,13 @@
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="str">
         <f aca="false">"重點觀察 2：收支關卡（FY2027–FY2031 自由現金流扣股利合計）情境 A／B／C 為 "&amp;TEXT(CF!C4,"0")&amp;"／"&amp;TEXT(CF!D4,"0")&amp;"／"&amp;TEXT(CF!E4,"0")&amp;" 十億美元；情境 B 需新增投資級債 "&amp;TEXT(CF!D5,"0")&amp;"、新股 "&amp;TEXT(CF!D6,"0")&amp;"、高息債 "&amp;TEXT(CF!D7,"0")&amp;"，調整後槓桿峰值 "&amp;TEXT(CF!D8,"0.00")&amp;" 倍。"</f>
-        <v>重點觀察 2：收支關卡（FY2027–FY2031 自由現金流扣股利合計）情境 A／B／C 為 136／98／25 十億美元；情境 B 需新增投資級債 14、新股 0、高息債 0，調整後槓桿峰值 3.82 倍。</v>
+        <v>重點觀察 2：收支關卡（FY2027–FY2031 自由現金流扣股利合計）情境 A／B／C 為 128／90／18 十億美元；情境 B 需新增投資級債 16、新股 0、高息債 0，調整後槓桿峰值 3.93 倍。</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="str">
-        <f aca="false">"重點觀察 3：DCF 情境加權 "&amp;TEXT(Val!C59,"0.0")&amp;"、分部加總 "&amp;TEXT(Val!C60,"0.0")&amp;"（OCI AI 只占分部企業價值的 "&amp;TEXT(Val!D53,"0%")&amp;"）：價值主要來自軟體與支援的現金流，AI 擴張本身接近不創造價值；市場共識目標價 "&amp;TEXT(cons_tp,"0")&amp;"，高出本模型 "&amp;TEXT(cons_tp/Val!C61-1,"0%")&amp;"。"</f>
-        <v>重點觀察 3：DCF 情境加權 62.6、分部加總 219.8（OCI AI 只占分部企業價值的 35%）：價值主要來自軟體與支援的現金流，AI 擴張本身接近不創造價值；市場共識目標價 237，高出本模型 68%。</v>
+        <f aca="false">"重點觀察 3：DCF 情境加權 "&amp;TEXT(Val!C59,"0.0")&amp;"、分部加總 "&amp;TEXT(Val!C60,"0.0")&amp;"（OCI AI 只占分部企業價值的 "&amp;TEXT(Val!D53,"0%")&amp;"）。兩法差距來自 AI 擴張：同業倍數把 OCI AI 的 EBITDA 當成價值，但 DCF 扣掉 AI 折舊與汰換後，AI 增量報酬低於資金成本；市場共識目標價 "&amp;TEXT(cons_tp,"0")&amp;"，高出本模型 "&amp;TEXT(cons_tp/Val!C61-1,"0%")&amp;"。"</f>
+        <v>重點觀察 3：DCF 情境加權 55.5、分部加總 211.0（OCI AI 只占分部企業價值的 36%）。兩法差距來自 AI 擴張：同業倍數把 OCI AI 的 EBITDA 當成價值，但 DCF 扣掉 AI 折舊與汰換後，AI 增量報酬低於資金成本；市場共識目標價 237，高出本模型 78%。</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38463,7 +39850,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -38514,6 +39901,780 @@
       </c>
       <c r="K3" s="6" t="s">
         <v>925</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>926</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>927</v>
+      </c>
+      <c r="C4" s="31" t="n">
+        <v>124.33500410432</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <f aca="false">C4/Val!$C$61-1</f>
+        <v>-0.0667800085096062</v>
+      </c>
+      <c r="E4" s="31" t="n">
+        <v>151.179494811617</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <f aca="false">E4/Val!$C$61-1</f>
+        <v>0.13470641576725</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <f aca="false">MAX(ABS(D4),ABS(F4))</f>
+        <v>0.13470641576725</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>-0.0404841488671738</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>0.218960647572229</v>
+      </c>
+      <c r="J4" s="32" t="n">
+        <v>70.9985422228601</v>
+      </c>
+      <c r="K4" s="32" t="n">
+        <v>128.297559041534</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>929</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>128.546165354244</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <f aca="false">C5/Val!$C$61-1</f>
+        <v>-0.0351723378127731</v>
+      </c>
+      <c r="E5" s="31" t="n">
+        <v>137.930476181898</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <f aca="false">E5/Val!$C$61-1</f>
+        <v>0.0352633897107377</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <f aca="false">MAX(ABS(D5),ABS(F5))</f>
+        <v>0.0352633897107377</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>0.0114048104207068</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>0.10999383306768</v>
+      </c>
+      <c r="J5" s="32" t="n">
+        <v>80.0164736659807</v>
+      </c>
+      <c r="K5" s="32" t="n">
+        <v>100.093224325263</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>931</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>125.674438522015</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <f aca="false">C6/Val!$C$61-1</f>
+        <v>-0.0567266290539343</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>139.652778918747</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <f aca="false">E6/Val!$C$61-1</f>
+        <v>0.0481904600639711</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <f aca="false">MAX(ABS(D6),ABS(F6))</f>
+        <v>0.0567266290539343</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>-0.0404886721736392</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>0.149389158238338</v>
+      </c>
+      <c r="J6" s="32" t="n">
+        <v>60.5525574013162</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>119.502407696795</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>932</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>933</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>130.505278423099</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <f aca="false">C7/Val!$C$61-1</f>
+        <v>-0.0204678425291149</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>135.288212267466</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <f aca="false">E7/Val!$C$61-1</f>
+        <v>0.01543137598697</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <f aca="false">MAX(ABS(D7),ABS(F7))</f>
+        <v>0.0204678425291149</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>0.0840038523918237</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>0.0436893404838652</v>
+      </c>
+      <c r="J7" s="32" t="n">
+        <v>102.494749710193</v>
+      </c>
+      <c r="K7" s="32" t="n">
+        <v>77.5777718497694</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>935</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>137.524828456276</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <f aca="false">C8/Val!$C$61-1</f>
+        <v>0.0322187236508449</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>122.907423125996</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <f aca="false">E8/Val!$C$61-1</f>
+        <v>-0.0774949887200511</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <f aca="false">MAX(ABS(D8),ABS(F8))</f>
+        <v>0.0774949887200511</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>0.0923694872846098</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>-0.00261453033450024</v>
+      </c>
+      <c r="J8" s="32" t="n">
+        <v>101.756661556217</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>67.8364785831964</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>936</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>937</v>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>124.09213988009</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <f aca="false">C9/Val!$C$61-1</f>
+        <v>-0.0686028720780917</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <v>139.753930898303</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <f aca="false">E9/Val!$C$61-1</f>
+        <v>0.0489496754609584</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <f aca="false">MAX(ABS(D9),ABS(F9))</f>
+        <v>0.0686028720780917</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>-0.0234007855347465</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>0.125218452025254</v>
+      </c>
+      <c r="J9" s="32" t="n">
+        <v>94.4980193013972</v>
+      </c>
+      <c r="K9" s="32" t="n">
+        <v>86.8698043727923</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>938</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>931</v>
+      </c>
+      <c r="C10" s="31" t="n">
+        <v>136.815553143013</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <f aca="false">C10/Val!$C$61-1</f>
+        <v>0.0268951230560173</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <v>129.648957343419</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <f aca="false">E10/Val!$C$61-1</f>
+        <v>-0.0268951230560173</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <f aca="false">MAX(ABS(D10),ABS(F10))</f>
+        <v>0.0268951230560173</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>0.102405197801497</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>0.0241823416156772</v>
+      </c>
+      <c r="J10" s="32" t="n">
+        <v>97.3771928139869</v>
+      </c>
+      <c r="K10" s="32" t="n">
+        <v>82.719261705435</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>939</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>940</v>
+      </c>
+      <c r="C11" s="31" t="n">
+        <v>127.978938097555</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <f aca="false">C11/Val!$C$61-1</f>
+        <v>-0.0394297697360977</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>137.364187802833</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <f aca="false">E11/Val!$C$61-1</f>
+        <v>0.0310130047117654</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <f aca="false">MAX(ABS(D11),ABS(F11))</f>
+        <v>0.0394297697360977</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>0.0385955878925062</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>0.0827923343002302</v>
+      </c>
+      <c r="J11" s="32" t="n">
+        <v>82.9912476201259</v>
+      </c>
+      <c r="K11" s="32" t="n">
+        <v>95.6195269751729</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>941</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>942</v>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>126.703739405429</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <f aca="false">C12/Val!$C$61-1</f>
+        <v>-0.0490010157515473</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>140.531505528064</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <f aca="false">E12/Val!$C$61-1</f>
+        <v>0.0547859095496297</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <f aca="false">MAX(ABS(D12),ABS(F12))</f>
+        <v>0.0547859095496297</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>0.0632336476767792</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>0.063351867189437</v>
+      </c>
+      <c r="J12" s="32" t="n">
+        <v>84.5222449133071</v>
+      </c>
+      <c r="K12" s="32" t="n">
+        <v>96.2188717265785</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>943</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>944</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>131.144726456037</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <f aca="false">C13/Val!$C$61-1</f>
+        <v>-0.0156683438508806</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <v>134.677085073215</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <f aca="false">E13/Val!$C$61-1</f>
+        <v>0.0108444447432152</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <f aca="false">MAX(ABS(D13),ABS(F13))</f>
+        <v>0.0156683438508806</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="J13" s="32" t="n">
+        <v>88.6720335861733</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>90.9865021677634</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>945</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>946</v>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>132.029397391643</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <f aca="false">C14/Val!$C$61-1</f>
+        <v>-0.00902827809509932</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <v>134.472402671385</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <f aca="false">E14/Val!$C$61-1</f>
+        <v>0.00930816209562102</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <f aca="false">MAX(ABS(D14),ABS(F14))</f>
+        <v>0.00930816209562102</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="J14" s="32" t="n">
+        <v>89.2052053978527</v>
+      </c>
+      <c r="K14" s="32" t="n">
+        <v>90.9073364589942</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>947</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>948</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>125.631737924948</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <f aca="false">C15/Val!$C$61-1</f>
+        <v>-0.0570471264964572</v>
+      </c>
+      <c r="E15" s="31" t="n">
+        <v>140.796613563307</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <f aca="false">E15/Val!$C$61-1</f>
+        <v>0.0567757282670194</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <f aca="false">MAX(ABS(D15),ABS(F15))</f>
+        <v>0.0570471264964572</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="J15" s="32" t="n">
+        <v>82.2258601358868</v>
+      </c>
+      <c r="K15" s="32" t="n">
+        <v>97.8705943835352</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>949</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>950</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>136.078572412212</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <f aca="false">C16/Val!$C$61-1</f>
+        <v>0.0213635741870468</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>130.228078228053</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <f aca="false">E16/Val!$C$61-1</f>
+        <v>-0.022548421248885</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <f aca="false">MAX(ABS(D16),ABS(F16))</f>
+        <v>0.022548421248885</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="J16" s="32" t="n">
+        <v>91.6880417003877</v>
+      </c>
+      <c r="K16" s="32" t="n">
+        <v>88.3441309752909</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>951</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>952</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>132.472629771595</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <f aca="false">C17/Val!$C$61-1</f>
+        <v>-0.00570151327270041</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <v>137.695258247781</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <f aca="false">E17/Val!$C$61-1</f>
+        <v>0.0334979168251544</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <f aca="false">MAX(ABS(D17),ABS(F17))</f>
+        <v>0.0334979168251544</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="J17" s="32" t="n">
+        <v>87.9170504091864</v>
+      </c>
+      <c r="K17" s="32" t="n">
+        <v>102.890178937499</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>953</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>954</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <v>139.531579851406</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <f aca="false">C18/Val!$C$61-1</f>
+        <v>0.047280777441548</v>
+      </c>
+      <c r="E18" s="31" t="n">
+        <v>128.702519860332</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <f aca="false">E18/Val!$C$61-1</f>
+        <v>-0.0339987893668464</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <f aca="false">MAX(ABS(D18),ABS(F18))</f>
+        <v>0.047280777441548</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="J18" s="32" t="n">
+        <v>90.048227259711</v>
+      </c>
+      <c r="K18" s="32" t="n">
+        <v>90.048227259711</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>956</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>130.122002680235</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <f aca="false">C19/Val!$C$61-1</f>
+        <v>-0.0233445914227244</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <v>137.099219328429</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <f aca="false">E19/Val!$C$61-1</f>
+        <v>0.0290242334947632</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <f aca="false">MAX(ABS(D19),ABS(F19))</f>
+        <v>0.0290242334947632</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="J19" s="32" t="n">
+        <v>90.048227259711</v>
+      </c>
+      <c r="K19" s="32" t="n">
+        <v>90.048227259711</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>957</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>931</v>
+      </c>
+      <c r="C20" s="31" t="n">
+        <v>108.431309824218</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <f aca="false">C20/Val!$C$61-1</f>
+        <v>-0.186148206931751</v>
+      </c>
+      <c r="E20" s="31" t="n">
+        <v>158.033200662214</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <f aca="false">E20/Val!$C$61-1</f>
+        <v>0.186148206931751</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <f aca="false">MAX(ABS(D20),ABS(F20))</f>
+        <v>0.186148206931751</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="J20" s="32" t="n">
+        <v>90.048227259711</v>
+      </c>
+      <c r="K20" s="32" t="n">
+        <v>90.048227259711</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>958</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>959</v>
+      </c>
+      <c r="C21" s="31" t="n">
+        <v>164.335247274284</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <f aca="false">C21/Val!$C$61-1</f>
+        <v>0.233449414890481</v>
+      </c>
+      <c r="E21" s="31" t="n">
+        <v>102.129263212148</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <f aca="false">E21/Val!$C$61-1</f>
+        <v>-0.233449414890481</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <f aca="false">MAX(ABS(D21),ABS(F21))</f>
+        <v>0.233449414890481</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>0.0632937697085872</v>
+      </c>
+      <c r="J21" s="32" t="n">
+        <v>90.048227259711</v>
+      </c>
+      <c r="K21" s="32" t="n">
+        <v>90.048227259711</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>960</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>961</v>
+      </c>
+      <c r="C22" s="31" t="n">
+        <v>137.783157867602</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <f aca="false">C22/Val!$C$61-1</f>
+        <v>0.0341576641187849</v>
+      </c>
+      <c r="E22" s="31" t="n">
+        <v>127.102799673962</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <f aca="false">E22/Val!$C$61-1</f>
+        <v>-0.0460057931021632</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <f aca="false">MAX(ABS(D22),ABS(F22))</f>
+        <v>0.0460057931021632</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>0.0602778586102519</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>0.0673149845063675</v>
+      </c>
+      <c r="J22" s="32" t="n">
+        <v>99.5283807949973</v>
+      </c>
+      <c r="K22" s="32" t="n">
+        <v>77.4080225459959</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>962</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>963</v>
+      </c>
+      <c r="C23" s="31" t="n">
+        <v>133.836991422715</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <f aca="false">C23/Val!$C$61-1</f>
+        <v>0.00453896226852146</v>
+      </c>
+      <c r="E23" s="31" t="n">
+        <v>132.614525819596</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <f aca="false">E23/Val!$C$61-1</f>
+        <v>-0.00463648553041707</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <f aca="false">MAX(ABS(D23),ABS(F23))</f>
+        <v>0.00463648553041707</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>0.0685689890063841</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>0.0580185504107903</v>
+      </c>
+      <c r="J23" s="32" t="n">
+        <v>92.5110068193853</v>
+      </c>
+      <c r="K23" s="32" t="n">
+        <v>87.5854477000366</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>964</v>
+      </c>
+      <c r="C25" s="33" t="n">
+        <f aca="false">133.232255243216-Val!C61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>965</v>
       </c>
     </row>
   </sheetData>
@@ -38543,21 +40704,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>926</v>
+        <v>966</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>927</v>
+        <v>967</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>928</v>
+        <v>968</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>774</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>929</v>
+        <v>969</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>22</v>
@@ -38568,13 +40729,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>930</v>
+        <v>970</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>931</v>
+        <v>971</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>932</v>
+        <v>972</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>29</v>
@@ -38585,13 +40746,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>933</v>
+        <v>973</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>934</v>
+        <v>974</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>935</v>
+        <v>975</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>35</v>
@@ -38602,13 +40763,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>936</v>
+        <v>976</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>937</v>
+        <v>977</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>938</v>
+        <v>978</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>35</v>
@@ -38619,13 +40780,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>939</v>
+        <v>979</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>940</v>
+        <v>980</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>941</v>
+        <v>981</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>35</v>
@@ -38636,16 +40797,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>942</v>
+        <v>982</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>788</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>943</v>
+        <v>983</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>944</v>
+        <v>984</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38653,16 +40814,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>945</v>
+        <v>985</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>946</v>
+        <v>986</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>947</v>
+        <v>987</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>944</v>
+        <v>984</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38670,13 +40831,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>948</v>
+        <v>988</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>946</v>
+        <v>986</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>949</v>
+        <v>989</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>35</v>
@@ -38687,13 +40848,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>950</v>
+        <v>990</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>951</v>
+        <v>991</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>952</v>
+        <v>992</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>29</v>
@@ -38704,13 +40865,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>953</v>
+        <v>993</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>954</v>
+        <v>994</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>955</v>
+        <v>995</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>29</v>
@@ -38721,13 +40882,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>956</v>
+        <v>996</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>946</v>
+        <v>986</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>957</v>
+        <v>997</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>40</v>
@@ -38738,13 +40899,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>958</v>
+        <v>998</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>959</v>
+        <v>999</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>40</v>
@@ -38755,13 +40916,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>961</v>
+        <v>1001</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>962</v>
+        <v>1002</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>963</v>
+        <v>1003</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>29</v>
@@ -38772,13 +40933,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>964</v>
+        <v>1004</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>965</v>
+        <v>1005</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>966</v>
+        <v>1006</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>35</v>
@@ -38789,13 +40950,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>967</v>
+        <v>1007</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>968</v>
+        <v>1008</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>969</v>
+        <v>1009</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>35</v>
@@ -38806,13 +40967,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>970</v>
+        <v>1010</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>788</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>971</v>
+        <v>1011</v>
       </c>
       <c r="E17" s="0" t="s">
         <v>35</v>
@@ -38823,13 +40984,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>972</v>
+        <v>1012</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>946</v>
+        <v>986</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>973</v>
+        <v>1013</v>
       </c>
       <c r="E18" s="0" t="s">
         <v>116</v>
@@ -38840,13 +41001,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>974</v>
+        <v>1014</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>951</v>
+        <v>991</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>975</v>
+        <v>1015</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>35</v>
@@ -38857,13 +41018,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>976</v>
+        <v>1016</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>116</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>977</v>
+        <v>1017</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>116</v>
@@ -47998,15 +50159,15 @@
       </c>
       <c r="C132" s="23" t="n">
         <f aca="false">CF!C4</f>
-        <v>135.829574748468</v>
+        <v>127.876572993986</v>
       </c>
       <c r="D132" s="23" t="n">
         <f aca="false">CF!D4</f>
-        <v>98.0012290141927</v>
+        <v>90.048227259711</v>
       </c>
       <c r="E132" s="23" t="n">
         <f aca="false">CF!E4</f>
-        <v>25.3630667286124</v>
+        <v>17.5198743091834</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>636</v>
@@ -51105,19 +53266,19 @@
       </c>
       <c r="F33" s="18" t="n">
         <f aca="false">CF!F46</f>
-        <v>5.73735087499617</v>
+        <v>5.83718502108689</v>
       </c>
       <c r="G33" s="18" t="n">
         <f aca="false">CF!G46</f>
-        <v>5.73735087499617</v>
+        <v>5.83718502108689</v>
       </c>
       <c r="H33" s="18" t="n">
         <f aca="false">CF!H46</f>
-        <v>5.73735087499617</v>
+        <v>5.83718502108689</v>
       </c>
       <c r="I33" s="18" t="n">
         <f aca="false">CF!I46</f>
-        <v>5.73735087499617</v>
+        <v>5.83718502108689</v>
       </c>
       <c r="J33" s="8" t="s">
         <v>674</v>
@@ -51144,15 +53305,15 @@
       </c>
       <c r="G34" s="18" t="n">
         <f aca="false">CF!G47</f>
-        <v>2.13793585352978</v>
+        <v>2.07344817740255</v>
       </c>
       <c r="H34" s="18" t="n">
         <f aca="false">CF!H47</f>
-        <v>4.04646231761855</v>
+        <v>3.91204030433779</v>
       </c>
       <c r="I34" s="18" t="n">
         <f aca="false">CF!I47</f>
-        <v>6.0681597616474</v>
+        <v>5.85843088790066</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>676</v>
@@ -51175,19 +53336,19 @@
       </c>
       <c r="F35" s="18" t="n">
         <f aca="false">F30-F33+F34</f>
-        <v>34.9787229883066</v>
+        <v>34.8788888422159</v>
       </c>
       <c r="G35" s="18" t="n">
         <f aca="false">G30-G33+G34</f>
-        <v>38.0779794808181</v>
+        <v>37.9136576586002</v>
       </c>
       <c r="H35" s="18" t="n">
         <f aca="false">H30-H33+H34</f>
-        <v>41.8439477982319</v>
+        <v>41.6096916388604</v>
       </c>
       <c r="I35" s="18" t="n">
         <f aca="false">I30-I33+I34</f>
-        <v>48.065868341954</v>
+        <v>47.7563053221165</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>678</v>
@@ -51210,19 +53371,19 @@
       </c>
       <c r="F36" s="18" t="n">
         <f aca="false">F35*etr</f>
-        <v>5.28178717123429</v>
+        <v>5.2667122151746</v>
       </c>
       <c r="G36" s="18" t="n">
         <f aca="false">G35*etr</f>
-        <v>5.74977490160353</v>
+        <v>5.72496230644862</v>
       </c>
       <c r="H36" s="18" t="n">
         <f aca="false">H35*etr</f>
-        <v>6.31843611753301</v>
+        <v>6.28306343746792</v>
       </c>
       <c r="I36" s="18" t="n">
         <f aca="false">I35*etr</f>
-        <v>7.25794611963505</v>
+        <v>7.21120210363959</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51246,19 +53407,19 @@
       </c>
       <c r="F37" s="18" t="n">
         <f aca="false">F35-F36</f>
-        <v>29.6969358170723</v>
+        <v>29.6121766270413</v>
       </c>
       <c r="G37" s="18" t="n">
         <f aca="false">G35-G36</f>
-        <v>32.3282045792146</v>
+        <v>32.1886953521515</v>
       </c>
       <c r="H37" s="18" t="n">
         <f aca="false">H35-H36</f>
-        <v>35.5255116806989</v>
+        <v>35.3266282013925</v>
       </c>
       <c r="I37" s="18" t="n">
         <f aca="false">I35-I36</f>
-        <v>40.8079222223189</v>
+        <v>40.5451032184769</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51320,19 +53481,19 @@
       </c>
       <c r="F39" s="18" t="n">
         <f aca="false">F37-F38</f>
-        <v>29.4529358170723</v>
+        <v>29.3681766270413</v>
       </c>
       <c r="G39" s="18" t="n">
         <f aca="false">G37-G38</f>
-        <v>32.3282045792146</v>
+        <v>32.1886953521515</v>
       </c>
       <c r="H39" s="18" t="n">
         <f aca="false">H37-H38</f>
-        <v>35.5255116806989</v>
+        <v>35.3266282013925</v>
       </c>
       <c r="I39" s="18" t="n">
         <f aca="false">I37-I38</f>
-        <v>40.8079222223189</v>
+        <v>40.5451032184769</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51390,19 +53551,19 @@
       </c>
       <c r="F41" s="19" t="n">
         <f aca="false">F39/F40</f>
-        <v>9.58331719475045</v>
+        <v>9.55573847701983</v>
       </c>
       <c r="G41" s="19" t="n">
         <f aca="false">G39/G40</f>
-        <v>10.4656771404403</v>
+        <v>10.4205135271943</v>
       </c>
       <c r="H41" s="19" t="n">
         <f aca="false">H39/H40</f>
-        <v>11.5007480414853</v>
+        <v>11.4363630776408</v>
       </c>
       <c r="I41" s="19" t="n">
         <f aca="false">I39/I40</f>
-        <v>13.2108338310128</v>
+        <v>13.125750886371</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51422,19 +53583,19 @@
       </c>
       <c r="F42" s="12" t="n">
         <f aca="false">F41/E41-1</f>
-        <v>0.145956384759881</v>
+        <v>0.142658569710598</v>
       </c>
       <c r="G42" s="12" t="n">
         <f aca="false">G41/F41-1</f>
-        <v>0.0920724972114275</v>
+        <v>0.0904979821553458</v>
       </c>
       <c r="H42" s="12" t="n">
         <f aca="false">H41/G41-1</f>
-        <v>0.0989014745204881</v>
+        <v>0.0974855555626368</v>
       </c>
       <c r="I42" s="12" t="n">
         <f aca="false">I41/H41-1</f>
-        <v>0.148693440057895</v>
+        <v>0.147720721811733</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51453,24 +53614,24 @@
         <v>20.2279737778082</v>
       </c>
       <c r="E43" s="18" t="n">
-        <f aca="false">Thesis!F27+nonai_cx*(E21-Thesis!F19)+amort</f>
-        <v>40.4761220288641</v>
+        <f aca="false">Thesis!F27+nonai_dep_q*(E21-Thesis!F19)/(q1_rev-Thesis!C19)+amort</f>
+        <v>38.7548436479898</v>
       </c>
       <c r="F43" s="18" t="n">
-        <f aca="false">Thesis!G27+nonai_cx*(F21-Thesis!G19)+amort</f>
-        <v>48.3783740984839</v>
+        <f aca="false">Thesis!G27+nonai_dep_q*(F21-Thesis!G19)/(q1_rev-Thesis!C19)+amort</f>
+        <v>46.5469957941759</v>
       </c>
       <c r="G43" s="18" t="n">
-        <f aca="false">Thesis!H27+nonai_cx*(G21-Thesis!H19)+amort</f>
-        <v>49.1580209020614</v>
+        <f aca="false">Thesis!H27+nonai_dep_q*(G21-Thesis!H19)/(q1_rev-Thesis!C19)+amort</f>
+        <v>47.2195547141434</v>
       </c>
       <c r="H43" s="18" t="n">
-        <f aca="false">Thesis!I27+nonai_cx*(H21-Thesis!I19)+amort</f>
-        <v>49.8941855726175</v>
+        <f aca="false">Thesis!I27+nonai_dep_q*(H21-Thesis!I19)/(q1_rev-Thesis!C19)+amort</f>
+        <v>47.8554585876367</v>
       </c>
       <c r="I43" s="18" t="n">
-        <f aca="false">Thesis!J27+nonai_cx*(I21-Thesis!J19)+amort</f>
-        <v>49.7498640268602</v>
+        <f aca="false">Thesis!J27+nonai_dep_q*(I21-Thesis!J19)/(q1_rev-Thesis!C19)+amort</f>
+        <v>47.6214666633468</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>687</v>
@@ -51529,23 +53690,23 @@
       </c>
       <c r="E45" s="18" t="n">
         <f aca="false">E30+E43</f>
-        <v>76.0989408388298</v>
+        <v>74.3776624579554</v>
       </c>
       <c r="F45" s="18" t="n">
         <f aca="false">F30+F43</f>
-        <v>88.7578976029646</v>
+        <v>86.9265192986566</v>
       </c>
       <c r="G45" s="18" t="n">
         <f aca="false">G30+G43</f>
-        <v>90.8354154043459</v>
+        <v>88.8969492164279</v>
       </c>
       <c r="H45" s="18" t="n">
         <f aca="false">H30+H43</f>
-        <v>93.429021928227</v>
+        <v>91.3902949432462</v>
       </c>
       <c r="I45" s="18" t="n">
         <f aca="false">I30+I43</f>
-        <v>97.4849234821629</v>
+        <v>95.3565261186496</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51565,23 +53726,23 @@
       </c>
       <c r="E46" s="18" t="n">
         <f aca="false">E45+E44</f>
-        <v>80.7872608388298</v>
+        <v>79.0659824579554</v>
       </c>
       <c r="F46" s="18" t="n">
         <f aca="false">F45+F44</f>
-        <v>93.6337504029646</v>
+        <v>91.8023720986566</v>
       </c>
       <c r="G46" s="18" t="n">
         <f aca="false">G45+G44</f>
-        <v>95.9063023163459</v>
+        <v>93.9678361284279</v>
       </c>
       <c r="H46" s="18" t="n">
         <f aca="false">H45+H44</f>
-        <v>98.702744316707</v>
+        <v>96.6640173317262</v>
       </c>
       <c r="I46" s="18" t="n">
         <f aca="false">I45+I44</f>
-        <v>102.969594766182</v>
+        <v>100.841197402669</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52436,19 +54597,19 @@
       </c>
       <c r="F73" s="18" t="n">
         <f aca="false">CF!F81</f>
-        <v>6.53447301147815</v>
+        <v>6.63430715756886</v>
       </c>
       <c r="G73" s="18" t="n">
         <f aca="false">CF!G81</f>
-        <v>6.53447301147815</v>
+        <v>6.63430715756886</v>
       </c>
       <c r="H73" s="18" t="n">
         <f aca="false">CF!H81</f>
-        <v>6.53447301147815</v>
+        <v>6.63430715756886</v>
       </c>
       <c r="I73" s="18" t="n">
         <f aca="false">CF!I81</f>
-        <v>6.53447301147815</v>
+        <v>6.63430715756886</v>
       </c>
       <c r="J73" s="8" t="s">
         <v>674</v>
@@ -52475,15 +54636,15 @@
       </c>
       <c r="G74" s="18" t="n">
         <f aca="false">CF!G82</f>
-        <v>1.40891729827141</v>
+        <v>1.34442962214419</v>
       </c>
       <c r="H74" s="18" t="n">
         <f aca="false">CF!H82</f>
-        <v>3.27723900356365</v>
+        <v>3.14281699028289</v>
       </c>
       <c r="I74" s="18" t="n">
         <f aca="false">CF!I82</f>
-        <v>5.25758291317863</v>
+        <v>5.04785403943188</v>
       </c>
       <c r="J74" s="8" t="s">
         <v>676</v>
@@ -52506,19 +54667,19 @@
       </c>
       <c r="F75" s="18" t="n">
         <f aca="false">F70-F73+F74</f>
-        <v>26.4041988683582</v>
+        <v>26.3043647222675</v>
       </c>
       <c r="G75" s="18" t="n">
         <f aca="false">G70-G73+G74</f>
-        <v>33.6751787202394</v>
+        <v>33.5108568980214</v>
       </c>
       <c r="H75" s="18" t="n">
         <f aca="false">H70-H73+H74</f>
-        <v>37.4009422788566</v>
+        <v>37.1666861194851</v>
       </c>
       <c r="I75" s="18" t="n">
         <f aca="false">I70-I73+I74</f>
-        <v>43.5815092881648</v>
+        <v>43.2719462683274</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>678</v>
@@ -52541,19 +54702,19 @@
       </c>
       <c r="F76" s="18" t="n">
         <f aca="false">F75*etr</f>
-        <v>3.98703402912209</v>
+        <v>3.97195907306239</v>
       </c>
       <c r="G76" s="18" t="n">
         <f aca="false">G75*etr</f>
-        <v>5.08495198675614</v>
+        <v>5.06013939160123</v>
       </c>
       <c r="H76" s="18" t="n">
         <f aca="false">H75*etr</f>
-        <v>5.64754228410734</v>
+        <v>5.61216960404225</v>
       </c>
       <c r="I76" s="18" t="n">
         <f aca="false">I75*etr</f>
-        <v>6.58080790251289</v>
+        <v>6.53406388651743</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52577,19 +54738,19 @@
       </c>
       <c r="F77" s="18" t="n">
         <f aca="false">F75-F76</f>
-        <v>22.4171648392361</v>
+        <v>22.3324056492051</v>
       </c>
       <c r="G77" s="18" t="n">
         <f aca="false">G75-G76</f>
-        <v>28.5902267334832</v>
+        <v>28.4507175064202</v>
       </c>
       <c r="H77" s="18" t="n">
         <f aca="false">H75-H76</f>
-        <v>31.7533999947492</v>
+        <v>31.5545165154429</v>
       </c>
       <c r="I77" s="18" t="n">
         <f aca="false">I75-I76</f>
-        <v>37.0007013856519</v>
+        <v>36.7378823818099</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52651,19 +54812,19 @@
       </c>
       <c r="F79" s="18" t="n">
         <f aca="false">F77-F78</f>
-        <v>22.1731648392361</v>
+        <v>22.0884056492051</v>
       </c>
       <c r="G79" s="18" t="n">
         <f aca="false">G77-G78</f>
-        <v>28.5902267334832</v>
+        <v>28.4507175064202</v>
       </c>
       <c r="H79" s="18" t="n">
         <f aca="false">H77-H78</f>
-        <v>31.7533999947492</v>
+        <v>31.5545165154429</v>
       </c>
       <c r="I79" s="18" t="n">
         <f aca="false">I77-I78</f>
-        <v>37.0007013856519</v>
+        <v>36.7378823818099</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52721,19 +54882,19 @@
       </c>
       <c r="F81" s="19" t="n">
         <f aca="false">F79/F80</f>
-        <v>7.21464485529205</v>
+        <v>7.18706613756142</v>
       </c>
       <c r="G81" s="19" t="n">
         <f aca="false">G79/G80</f>
-        <v>9.25557377092951</v>
+        <v>9.21041015768349</v>
       </c>
       <c r="H81" s="19" t="n">
         <f aca="false">H79/H80</f>
-        <v>10.27959445264</v>
+        <v>10.2152094887956</v>
       </c>
       <c r="I81" s="19" t="n">
         <f aca="false">I79/I80</f>
-        <v>11.9783142835297</v>
+        <v>11.8932313388879</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52753,19 +54914,19 @@
       </c>
       <c r="F82" s="12" t="n">
         <f aca="false">F81/E81-1</f>
-        <v>0.357986721811882</v>
+        <v>0.352795678699716</v>
       </c>
       <c r="G82" s="12" t="n">
         <f aca="false">G81/F81-1</f>
-        <v>0.28288695515489</v>
+        <v>0.281525727104076</v>
       </c>
       <c r="H82" s="12" t="n">
         <f aca="false">H81/G81-1</f>
-        <v>0.110638271278957</v>
+        <v>0.109093874638567</v>
       </c>
       <c r="I82" s="12" t="n">
         <f aca="false">I81/H81-1</f>
-        <v>0.165251638935371</v>
+        <v>0.164267003230118</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52784,24 +54945,24 @@
         <v>20.2279737778082</v>
       </c>
       <c r="E83" s="18" t="n">
-        <f aca="false">Thesis!F62+nonai_cx*(E61-Thesis!F54)+amort</f>
-        <v>40.4898303621974</v>
+        <f aca="false">Thesis!F62+nonai_dep_q*(E61-Thesis!F54)/(q1_rev-Thesis!C54)+amort</f>
+        <v>38.7685519813231</v>
       </c>
       <c r="F83" s="18" t="n">
-        <f aca="false">Thesis!G62+nonai_cx*(F61-Thesis!G54)+amort</f>
-        <v>50.1872295151506</v>
+        <f aca="false">Thesis!G62+nonai_dep_q*(F61-Thesis!G54)/(q1_rev-Thesis!C54)+amort</f>
+        <v>48.3558512108426</v>
       </c>
       <c r="G83" s="18" t="n">
-        <f aca="false">Thesis!H62+nonai_cx*(G61-Thesis!H54)+amort</f>
-        <v>52.7483150687281</v>
+        <f aca="false">Thesis!H62+nonai_dep_q*(G61-Thesis!H54)/(q1_rev-Thesis!C54)+amort</f>
+        <v>50.80984888081</v>
       </c>
       <c r="H83" s="18" t="n">
-        <f aca="false">Thesis!I62+nonai_cx*(H61-Thesis!I54)+amort</f>
-        <v>53.4844797392841</v>
+        <f aca="false">Thesis!I62+nonai_dep_q*(H61-Thesis!I54)/(q1_rev-Thesis!C54)+amort</f>
+        <v>51.4457527543033</v>
       </c>
       <c r="I83" s="18" t="n">
-        <f aca="false">Thesis!J62+nonai_cx*(I61-Thesis!J54)+amort</f>
-        <v>53.3401581935269</v>
+        <f aca="false">Thesis!J62+nonai_dep_q*(I61-Thesis!J54)/(q1_rev-Thesis!C54)+amort</f>
+        <v>51.2117608300135</v>
       </c>
       <c r="J83" s="8" t="s">
         <v>687</v>
@@ -52860,23 +55021,23 @@
       </c>
       <c r="E85" s="18" t="n">
         <f aca="false">E70+E83</f>
-        <v>65.2728854991712</v>
+        <v>63.5516071182969</v>
       </c>
       <c r="F85" s="18" t="n">
         <f aca="false">F70+F83</f>
-        <v>82.7893510361649</v>
+        <v>80.9579727318568</v>
       </c>
       <c r="G85" s="18" t="n">
         <f aca="false">G70+G83</f>
-        <v>91.5490495021742</v>
+        <v>89.6105833142561</v>
       </c>
       <c r="H85" s="18" t="n">
         <f aca="false">H70+H83</f>
-        <v>94.1426560260552</v>
+        <v>92.1039290410744</v>
       </c>
       <c r="I85" s="18" t="n">
         <f aca="false">I70+I83</f>
-        <v>98.1985575799912</v>
+        <v>96.0701602164778</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52896,23 +55057,23 @@
       </c>
       <c r="E86" s="18" t="n">
         <f aca="false">E85+E84</f>
-        <v>69.9612054991712</v>
+        <v>68.2399271182969</v>
       </c>
       <c r="F86" s="18" t="n">
         <f aca="false">F85+F84</f>
-        <v>87.6652038361649</v>
+        <v>85.8338255318568</v>
       </c>
       <c r="G86" s="18" t="n">
         <f aca="false">G85+G84</f>
-        <v>96.6199364141742</v>
+        <v>94.6814702262561</v>
       </c>
       <c r="H86" s="18" t="n">
         <f aca="false">H85+H84</f>
-        <v>99.4163784145352</v>
+        <v>97.3776514295544</v>
       </c>
       <c r="I86" s="18" t="n">
         <f aca="false">I85+I84</f>
-        <v>103.68322886401</v>
+        <v>101.554831500497</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53802,19 +55963,19 @@
       </c>
       <c r="F114" s="18" t="n">
         <f aca="false">CF!F117</f>
-        <v>0.404368772598643</v>
+        <v>0.346439086927049</v>
       </c>
       <c r="G114" s="18" t="n">
         <f aca="false">CF!G117</f>
-        <v>0.524718579174098</v>
+        <v>0.403498558780336</v>
       </c>
       <c r="H114" s="18" t="n">
         <f aca="false">CF!H117</f>
-        <v>0.976995117957945</v>
+        <v>0.787072313601897</v>
       </c>
       <c r="I114" s="18" t="n">
         <f aca="false">CF!I117</f>
-        <v>2.33569539101492</v>
+        <v>2.07173246870798</v>
       </c>
       <c r="J114" s="8" t="s">
         <v>676</v>
@@ -53837,19 +55998,19 @@
       </c>
       <c r="F115" s="18" t="n">
         <f aca="false">F110-F113+F114</f>
-        <v>4.34713725370224</v>
+        <v>4.28920756803064</v>
       </c>
       <c r="G115" s="18" t="n">
         <f aca="false">G110-G113+G114</f>
-        <v>8.74849579891569</v>
+        <v>8.62727577852193</v>
       </c>
       <c r="H115" s="18" t="n">
         <f aca="false">H110-H113+H114</f>
-        <v>17.6984790361182</v>
+        <v>17.5085562317621</v>
       </c>
       <c r="I115" s="18" t="n">
         <f aca="false">I110-I113+I114</f>
-        <v>23.2574024088684</v>
+        <v>22.9934394865614</v>
       </c>
       <c r="J115" s="5" t="s">
         <v>678</v>
@@ -53872,19 +56033,19 @@
       </c>
       <c r="F116" s="18" t="n">
         <f aca="false">F115*etr</f>
-        <v>0.656417725309038</v>
+        <v>0.647670342772627</v>
       </c>
       <c r="G116" s="18" t="n">
         <f aca="false">G115*etr</f>
-        <v>1.32102286563627</v>
+        <v>1.30271864255681</v>
       </c>
       <c r="H116" s="18" t="n">
         <f aca="false">H115*etr</f>
-        <v>2.67247033445384</v>
+        <v>2.64379199099608</v>
       </c>
       <c r="I116" s="18" t="n">
         <f aca="false">I115*etr</f>
-        <v>3.51186776373912</v>
+        <v>3.47200936247078</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53908,19 +56069,19 @@
       </c>
       <c r="F117" s="18" t="n">
         <f aca="false">F115-F116</f>
-        <v>3.6907195283932</v>
+        <v>3.64153722525802</v>
       </c>
       <c r="G117" s="18" t="n">
         <f aca="false">G115-G116</f>
-        <v>7.42747293327942</v>
+        <v>7.32455713596512</v>
       </c>
       <c r="H117" s="18" t="n">
         <f aca="false">H115-H116</f>
-        <v>15.0260087016643</v>
+        <v>14.864764240766</v>
       </c>
       <c r="I117" s="18" t="n">
         <f aca="false">I115-I116</f>
-        <v>19.7455346451292</v>
+        <v>19.5214301240907</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53982,19 +56143,19 @@
       </c>
       <c r="F119" s="18" t="n">
         <f aca="false">F117-F118</f>
-        <v>3.4467195283932</v>
+        <v>3.39753722525802</v>
       </c>
       <c r="G119" s="18" t="n">
         <f aca="false">G117-G118</f>
-        <v>7.42747293327942</v>
+        <v>7.32455713596512</v>
       </c>
       <c r="H119" s="18" t="n">
         <f aca="false">H117-H118</f>
-        <v>15.0260087016643</v>
+        <v>14.864764240766</v>
       </c>
       <c r="I119" s="18" t="n">
         <f aca="false">I117-I118</f>
-        <v>19.7455346451292</v>
+        <v>19.5214301240907</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54052,19 +56213,19 @@
       </c>
       <c r="F121" s="19" t="n">
         <f aca="false">F119/F120</f>
-        <v>1.12148434801486</v>
+        <v>1.10548154224228</v>
       </c>
       <c r="G121" s="19" t="n">
         <f aca="false">G119/G120</f>
-        <v>2.4045113145269</v>
+        <v>2.37119416866737</v>
       </c>
       <c r="H121" s="19" t="n">
         <f aca="false">H119/H120</f>
-        <v>4.86440115768677</v>
+        <v>4.81220115182777</v>
       </c>
       <c r="I121" s="19" t="n">
         <f aca="false">I119/I120</f>
-        <v>6.39226314146032</v>
+        <v>6.31971331713723</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54084,19 +56245,19 @@
       </c>
       <c r="F122" s="12" t="n">
         <f aca="false">F121/E121-1</f>
-        <v>-0.239906530922477</v>
+        <v>-0.250752538872729</v>
       </c>
       <c r="G122" s="12" t="n">
         <f aca="false">G121/F121-1</f>
-        <v>1.1440435783015</v>
+        <v>1.14494234237309</v>
       </c>
       <c r="H122" s="12" t="n">
         <f aca="false">H121/G121-1</f>
-        <v>1.02303109504971</v>
+        <v>1.02944204882735</v>
       </c>
       <c r="I122" s="12" t="n">
         <f aca="false">I121/H121-1</f>
-        <v>0.314090457231147</v>
+        <v>0.31326873456586</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54115,24 +56276,24 @@
         <v>20.2279737778082</v>
       </c>
       <c r="E123" s="18" t="n">
-        <f aca="false">Thesis!F97+nonai_cx*(E101-Thesis!F89)+amort</f>
-        <v>36.7195841621974</v>
+        <f aca="false">Thesis!F97+nonai_dep_q*(E101-Thesis!F89)/(q1_rev-Thesis!C89)+amort</f>
+        <v>34.9983057813231</v>
       </c>
       <c r="F123" s="18" t="n">
-        <f aca="false">Thesis!G97+nonai_cx*(F101-Thesis!G89)+amort</f>
-        <v>43.1686790926506</v>
+        <f aca="false">Thesis!G97+nonai_dep_q*(F101-Thesis!G89)/(q1_rev-Thesis!C89)+amort</f>
+        <v>41.3373007883426</v>
       </c>
       <c r="G123" s="18" t="n">
-        <f aca="false">Thesis!H97+nonai_cx*(G101-Thesis!H89)+amort</f>
-        <v>48.2693132537281</v>
+        <f aca="false">Thesis!H97+nonai_dep_q*(G101-Thesis!H89)/(q1_rev-Thesis!C89)+amort</f>
+        <v>46.33084706581</v>
       </c>
       <c r="H123" s="18" t="n">
-        <f aca="false">Thesis!I97+nonai_cx*(H101-Thesis!I89)+amort</f>
-        <v>51.0230845542841</v>
+        <f aca="false">Thesis!I97+nonai_dep_q*(H101-Thesis!I89)/(q1_rev-Thesis!C89)+amort</f>
+        <v>48.9843575693033</v>
       </c>
       <c r="I123" s="18" t="n">
-        <f aca="false">Thesis!J97+nonai_cx*(I101-Thesis!J89)+amort</f>
-        <v>50.8787630085269</v>
+        <f aca="false">Thesis!J97+nonai_dep_q*(I101-Thesis!J89)/(q1_rev-Thesis!C89)+amort</f>
+        <v>48.7503656450135</v>
       </c>
       <c r="J123" s="8" t="s">
         <v>687</v>
@@ -54191,23 +56352,23 @@
       </c>
       <c r="E125" s="18" t="n">
         <f aca="false">E110+E123</f>
-        <v>47.7681451163055</v>
+        <v>46.0468667354311</v>
       </c>
       <c r="F125" s="18" t="n">
         <f aca="false">F110+F123</f>
-        <v>52.8234475737542</v>
+        <v>50.9920692694462</v>
       </c>
       <c r="G125" s="18" t="n">
         <f aca="false">G110+G123</f>
-        <v>62.2050904734697</v>
+        <v>60.2666242855516</v>
       </c>
       <c r="H125" s="18" t="n">
         <f aca="false">H110+H123</f>
-        <v>73.4565684724443</v>
+        <v>71.4178414874635</v>
       </c>
       <c r="I125" s="18" t="n">
         <f aca="false">I110+I123</f>
-        <v>77.5124700263803</v>
+        <v>75.3840726628669</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54227,23 +56388,23 @@
       </c>
       <c r="E126" s="18" t="n">
         <f aca="false">E125+E124</f>
-        <v>52.4564651163055</v>
+        <v>50.7351867354311</v>
       </c>
       <c r="F126" s="18" t="n">
         <f aca="false">F125+F124</f>
-        <v>57.6993003737542</v>
+        <v>55.8679220694462</v>
       </c>
       <c r="G126" s="18" t="n">
         <f aca="false">G125+G124</f>
-        <v>67.2759773854697</v>
+        <v>65.3375111975516</v>
       </c>
       <c r="H126" s="18" t="n">
         <f aca="false">H125+H124</f>
-        <v>78.7302908609243</v>
+        <v>76.6915638759435</v>
       </c>
       <c r="I126" s="18" t="n">
         <f aca="false">I125+I124</f>
-        <v>82.9971413103995</v>
+        <v>80.8687439468861</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54324,15 +56485,15 @@
       </c>
       <c r="C4" s="23" t="n">
         <f aca="false">SUM(D26:H26)</f>
-        <v>135.829574748468</v>
+        <v>127.876572993986</v>
       </c>
       <c r="D4" s="23" t="n">
         <f aca="false">SUM(D61:H61)</f>
-        <v>98.0012290141927</v>
+        <v>90.048227259711</v>
       </c>
       <c r="E4" s="23" t="n">
         <f aca="false">SUM(D96:H96)</f>
-        <v>25.3630667286124</v>
+        <v>17.5198743091834</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>694</v>
@@ -54347,11 +56508,11 @@
       </c>
       <c r="C5" s="23" t="n">
         <f aca="false">SUM(D34:H34)</f>
-        <v>0.437084051658159</v>
+        <v>2.1583624325325</v>
       </c>
       <c r="D5" s="23" t="n">
         <f aca="false">SUM(D69:H69)</f>
-        <v>14.1805691634164</v>
+        <v>15.9018475442907</v>
       </c>
       <c r="E5" s="23" t="n">
         <f aca="false">SUM(D104:H104)</f>
@@ -54407,15 +56568,15 @@
       </c>
       <c r="C8" s="19" t="n">
         <f aca="false">MAX(D41:H41)</f>
-        <v>3.2528477988063</v>
+        <v>3.32531252142553</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">MAX(D76:H76)</f>
-        <v>3.81864058802246</v>
+        <v>3.92716649109788</v>
       </c>
       <c r="E8" s="19" t="n">
         <f aca="false">MAX(D111:H111)</f>
-        <v>4.87342534480852</v>
+        <v>5.00087725008708</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54447,15 +56608,15 @@
       </c>
       <c r="C10" s="23" t="n">
         <f aca="false">SUM(D24:H24)</f>
-        <v>167.058018748468</v>
+        <v>159.105016993986</v>
       </c>
       <c r="D10" s="23" t="n">
         <f aca="false">SUM(D59:H59)</f>
-        <v>129.229673014193</v>
+        <v>121.276671259711</v>
       </c>
       <c r="E10" s="23" t="n">
         <f aca="false">SUM(D94:H94)</f>
-        <v>56.5915107286124</v>
+        <v>48.7483183091834</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54516,19 +56677,19 @@
       </c>
       <c r="F15" s="18" t="n">
         <f aca="false">PL!F37</f>
-        <v>29.6969358170723</v>
+        <v>29.6121766270413</v>
       </c>
       <c r="G15" s="18" t="n">
         <f aca="false">PL!G37</f>
-        <v>32.3282045792146</v>
+        <v>32.1886953521515</v>
       </c>
       <c r="H15" s="18" t="n">
         <f aca="false">PL!H37</f>
-        <v>35.5255116806989</v>
+        <v>35.3266282013925</v>
       </c>
       <c r="I15" s="18" t="n">
         <f aca="false">PL!I37</f>
-        <v>40.8079222223189</v>
+        <v>40.5451032184769</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54548,23 +56709,23 @@
       </c>
       <c r="E16" s="18" t="n">
         <f aca="false">PL!E43</f>
-        <v>40.4761220288641</v>
+        <v>38.7548436479898</v>
       </c>
       <c r="F16" s="18" t="n">
         <f aca="false">PL!F43</f>
-        <v>48.3783740984839</v>
+        <v>46.5469957941759</v>
       </c>
       <c r="G16" s="18" t="n">
         <f aca="false">PL!G43</f>
-        <v>49.1580209020614</v>
+        <v>47.2195547141434</v>
       </c>
       <c r="H16" s="18" t="n">
         <f aca="false">PL!H43</f>
-        <v>49.8941855726175</v>
+        <v>47.8554585876367</v>
       </c>
       <c r="I16" s="18" t="n">
         <f aca="false">PL!I43</f>
-        <v>49.7498640268602</v>
+        <v>47.6214666633468</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54690,23 +56851,23 @@
       </c>
       <c r="E20" s="18" t="n">
         <f aca="false">E15+E16+E17+E18-E19</f>
-        <v>84.6093378229231</v>
+        <v>82.8880594420487</v>
       </c>
       <c r="F20" s="18" t="n">
         <f aca="false">F15+F16+F17+F18-F19</f>
-        <v>75.2899942848226</v>
+        <v>73.3738567904835</v>
       </c>
       <c r="G20" s="18" t="n">
         <f aca="false">G15+G16+G17+G18-G19</f>
-        <v>78.3529120054263</v>
+        <v>76.2749365904453</v>
       </c>
       <c r="H20" s="18" t="n">
         <f aca="false">H15+H16+H17+H18-H19</f>
-        <v>82.0246896880747</v>
+        <v>79.7870792237875</v>
       </c>
       <c r="I20" s="18" t="n">
         <f aca="false">I15+I16+I17+I18-I19</f>
-        <v>99.7543632457247</v>
+        <v>97.3631468783693</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>707</v>
@@ -54832,23 +56993,23 @@
       </c>
       <c r="E24" s="18" t="n">
         <f aca="false">E20-E23</f>
-        <v>-1.62368816511926</v>
+        <v>-3.3449665459936</v>
       </c>
       <c r="F24" s="18" t="n">
         <f aca="false">F20-F23</f>
-        <v>59.8164630596604</v>
+        <v>57.9003255653214</v>
       </c>
       <c r="G24" s="18" t="n">
         <f aca="false">G20-G23</f>
-        <v>62.8184438925201</v>
+        <v>60.740468477539</v>
       </c>
       <c r="H24" s="18" t="n">
         <f aca="false">H20-H23</f>
-        <v>66.1811198479457</v>
+        <v>63.9435093836585</v>
       </c>
       <c r="I24" s="18" t="n">
         <f aca="false">I20-I23</f>
-        <v>40.6223448546863</v>
+        <v>38.2311284873309</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54904,23 +57065,23 @@
       </c>
       <c r="E26" s="18" t="n">
         <f aca="false">E24-E25</f>
-        <v>-7.99616016511926</v>
+        <v>-9.7174385459936</v>
       </c>
       <c r="F26" s="18" t="n">
         <f aca="false">F24-F25</f>
-        <v>53.5249910596604</v>
+        <v>51.6088535653214</v>
       </c>
       <c r="G26" s="18" t="n">
         <f aca="false">G24-G25</f>
-        <v>56.7084958925201</v>
+        <v>54.630520477539</v>
       </c>
       <c r="H26" s="18" t="n">
         <f aca="false">H24-H25</f>
-        <v>60.0711718479457</v>
+        <v>57.8335613836585</v>
       </c>
       <c r="I26" s="18" t="n">
         <f aca="false">I24-I25</f>
-        <v>34.5123968546863</v>
+        <v>32.1211804873309</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54970,15 +57131,15 @@
       </c>
       <c r="G28" s="18" t="n">
         <f aca="false">F37</f>
-        <v>63.5249910596604</v>
+        <v>61.6088535653214</v>
       </c>
       <c r="H28" s="18" t="n">
         <f aca="false">G37</f>
-        <v>120.233486952181</v>
+        <v>116.23937404286</v>
       </c>
       <c r="I28" s="18" t="n">
         <f aca="false">H37</f>
-        <v>180.304658800126</v>
+        <v>174.072935426519</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54994,23 +57155,23 @@
       </c>
       <c r="E29" s="18" t="n">
         <f aca="false">E26</f>
-        <v>-7.99616016511926</v>
+        <v>-9.7174385459936</v>
       </c>
       <c r="F29" s="18" t="n">
         <f aca="false">F26</f>
-        <v>53.5249910596604</v>
+        <v>51.6088535653214</v>
       </c>
       <c r="G29" s="18" t="n">
         <f aca="false">G26</f>
-        <v>56.7084958925201</v>
+        <v>54.630520477539</v>
       </c>
       <c r="H29" s="18" t="n">
         <f aca="false">H26</f>
-        <v>60.0711718479457</v>
+        <v>57.8335613836585</v>
       </c>
       <c r="I29" s="18" t="n">
         <f aca="false">I26</f>
-        <v>34.5123968546863</v>
+        <v>32.1211804873309</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55026,7 +57187,7 @@
       </c>
       <c r="E30" s="18" t="n">
         <f aca="false">MAX(0,-(E29+E28-min_cash))</f>
-        <v>0.437084051658159</v>
+        <v>2.1583624325325</v>
       </c>
       <c r="F30" s="18" t="n">
         <f aca="false">MAX(0,-(F29+F28-min_cash))</f>
@@ -55058,23 +57219,23 @@
       </c>
       <c r="E31" s="18" t="n">
         <f aca="false">PL!E45+Thesis!F22+rent_on</f>
-        <v>88.9735290741239</v>
+        <v>87.2522506932495</v>
       </c>
       <c r="F31" s="18" t="n">
         <f aca="false">PL!F45+Thesis!G22+rent_on</f>
-        <v>107.792913645745</v>
+        <v>105.961535341437</v>
       </c>
       <c r="G31" s="18" t="n">
         <f aca="false">PL!G45+Thesis!H22+rent_on</f>
-        <v>112.180591874934</v>
+        <v>110.242125687016</v>
       </c>
       <c r="H31" s="18" t="n">
         <f aca="false">PL!H45+Thesis!I22+rent_on</f>
-        <v>114.774198398815</v>
+        <v>112.735471413834</v>
       </c>
       <c r="I31" s="18" t="n">
         <f aca="false">PL!I45+Thesis!J22+rent_on</f>
-        <v>118.830099952751</v>
+        <v>116.701702589238</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>720</v>
@@ -55128,23 +57289,23 @@
       </c>
       <c r="E33" s="18" t="n">
         <f aca="false">MAX(0,lev_max*E31/E27-E32-(debt_q1+D38))</f>
-        <v>116.144334943125</v>
+        <v>108.398582229191</v>
       </c>
       <c r="F33" s="18" t="n">
         <f aca="false">MAX(0,lev_max*F31/F27-F32-(debt_q1+E38))</f>
-        <v>134.434169526374</v>
+        <v>124.471688776113</v>
       </c>
       <c r="G33" s="18" t="n">
         <f aca="false">MAX(0,lev_max*G31/G27-G32-(debt_q1+F38))</f>
-        <v>154.178721557723</v>
+        <v>143.734345331218</v>
       </c>
       <c r="H33" s="18" t="n">
         <f aca="false">MAX(0,lev_max*H31/H27-H32-(debt_q1+G38))</f>
-        <v>165.849950915188</v>
+        <v>154.9544011019</v>
       </c>
       <c r="I33" s="18" t="n">
         <f aca="false">MAX(0,lev_max*I31/I27-I32-(debt_q1+H38))</f>
-        <v>184.1015079079</v>
+        <v>172.802441391215</v>
       </c>
       <c r="J33" s="8" t="s">
         <v>724</v>
@@ -55163,7 +57324,7 @@
       </c>
       <c r="E34" s="18" t="n">
         <f aca="false">MIN(E30,E33)</f>
-        <v>0.437084051658159</v>
+        <v>2.1583624325325</v>
       </c>
       <c r="F34" s="18" t="n">
         <f aca="false">MIN(F30,F33)</f>
@@ -55263,19 +57424,19 @@
       </c>
       <c r="F37" s="18" t="n">
         <f aca="false">F28+F29+F34+F35+F36</f>
-        <v>63.5249910596604</v>
+        <v>61.6088535653214</v>
       </c>
       <c r="G37" s="18" t="n">
         <f aca="false">G28+G29+G34+G35+G36</f>
-        <v>120.233486952181</v>
+        <v>116.23937404286</v>
       </c>
       <c r="H37" s="18" t="n">
         <f aca="false">H28+H29+H34+H35+H36</f>
-        <v>180.304658800126</v>
+        <v>174.072935426519</v>
       </c>
       <c r="I37" s="18" t="n">
         <f aca="false">I28+I29+I34+I35+I36</f>
-        <v>214.817055654812</v>
+        <v>206.19411591385</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55291,23 +57452,23 @@
       </c>
       <c r="E38" s="18" t="n">
         <f aca="false">D38+E34</f>
-        <v>0.437084051658159</v>
+        <v>2.1583624325325</v>
       </c>
       <c r="F38" s="18" t="n">
         <f aca="false">E38+F34</f>
-        <v>0.437084051658159</v>
+        <v>2.1583624325325</v>
       </c>
       <c r="G38" s="18" t="n">
         <f aca="false">F38+G34</f>
-        <v>0.437084051658159</v>
+        <v>2.1583624325325</v>
       </c>
       <c r="H38" s="18" t="n">
         <f aca="false">G38+H34</f>
-        <v>0.437084051658159</v>
+        <v>2.1583624325325</v>
       </c>
       <c r="I38" s="18" t="n">
         <f aca="false">H38+I34</f>
-        <v>0.437084051658159</v>
+        <v>2.1583624325325</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55355,23 +57516,23 @@
       </c>
       <c r="E40" s="18" t="n">
         <f aca="false">debt_q1+E38+E39</f>
-        <v>125.437084051658</v>
+        <v>127.158362432533</v>
       </c>
       <c r="F40" s="18" t="n">
         <f aca="false">debt_q1+F38+F39</f>
-        <v>125.437084051658</v>
+        <v>127.158362432533</v>
       </c>
       <c r="G40" s="18" t="n">
         <f aca="false">debt_q1+G38+G39</f>
-        <v>125.437084051658</v>
+        <v>127.158362432533</v>
       </c>
       <c r="H40" s="18" t="n">
         <f aca="false">debt_q1+H38+H39</f>
-        <v>125.437084051658</v>
+        <v>127.158362432533</v>
       </c>
       <c r="I40" s="18" t="n">
         <f aca="false">debt_q1+I38+I39</f>
-        <v>125.437084051658</v>
+        <v>127.158362432533</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55387,23 +57548,23 @@
       </c>
       <c r="E41" s="19" t="n">
         <f aca="false">(E40+E32)/(E31/E27)</f>
-        <v>3.19953173606196</v>
+        <v>3.28237846069823</v>
       </c>
       <c r="F41" s="19" t="n">
         <f aca="false">(F40+F32)/(F31/F27)</f>
-        <v>3.2528477988063</v>
+        <v>3.32531252142553</v>
       </c>
       <c r="G41" s="19" t="n">
         <f aca="false">(G40+G32)/(G31/G27)</f>
-        <v>3.12562035927203</v>
+        <v>3.19619399630149</v>
       </c>
       <c r="H41" s="19" t="n">
         <f aca="false">(H40+H32)/(H31/H27)</f>
-        <v>3.05498924646029</v>
+        <v>3.12550447380411</v>
       </c>
       <c r="I41" s="19" t="n">
         <f aca="false">(I40+I32)/(I31/I27)</f>
-        <v>2.95071654419965</v>
+        <v>3.01928088830513</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55557,19 +57718,19 @@
       </c>
       <c r="F46" s="18" t="n">
         <f aca="false">r_old*debt_q1+r_new*E38+r_junk*E39</f>
-        <v>5.73735087499617</v>
+        <v>5.83718502108689</v>
       </c>
       <c r="G46" s="18" t="n">
         <f aca="false">r_old*debt_q1+r_new*F38+r_junk*F39</f>
-        <v>5.73735087499617</v>
+        <v>5.83718502108689</v>
       </c>
       <c r="H46" s="18" t="n">
         <f aca="false">r_old*debt_q1+r_new*G38+r_junk*G39</f>
-        <v>5.73735087499617</v>
+        <v>5.83718502108689</v>
       </c>
       <c r="I46" s="18" t="n">
         <f aca="false">r_old*debt_q1+r_new*H38+r_junk*H39</f>
-        <v>5.73735087499617</v>
+        <v>5.83718502108689</v>
       </c>
       <c r="J46" s="8" t="s">
         <v>739</v>
@@ -55596,15 +57757,15 @@
       </c>
       <c r="G47" s="18" t="n">
         <f aca="false">r_cash*G28</f>
-        <v>2.13793585352978</v>
+        <v>2.07344817740255</v>
       </c>
       <c r="H47" s="18" t="n">
         <f aca="false">r_cash*H28</f>
-        <v>4.04646231761855</v>
+        <v>3.91204030433779</v>
       </c>
       <c r="I47" s="18" t="n">
         <f aca="false">r_cash*I28</f>
-        <v>6.0681597616474</v>
+        <v>5.85843088790066</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55633,19 +57794,19 @@
       </c>
       <c r="F50" s="18" t="n">
         <f aca="false">PL!F77</f>
-        <v>22.4171648392361</v>
+        <v>22.3324056492051</v>
       </c>
       <c r="G50" s="18" t="n">
         <f aca="false">PL!G77</f>
-        <v>28.5902267334832</v>
+        <v>28.4507175064202</v>
       </c>
       <c r="H50" s="18" t="n">
         <f aca="false">PL!H77</f>
-        <v>31.7533999947492</v>
+        <v>31.5545165154429</v>
       </c>
       <c r="I50" s="18" t="n">
         <f aca="false">PL!I77</f>
-        <v>37.0007013856519</v>
+        <v>36.7378823818099</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55665,23 +57826,23 @@
       </c>
       <c r="E51" s="18" t="n">
         <f aca="false">PL!E83</f>
-        <v>40.4898303621974</v>
+        <v>38.7685519813231</v>
       </c>
       <c r="F51" s="18" t="n">
         <f aca="false">PL!F83</f>
-        <v>50.1872295151506</v>
+        <v>48.3558512108426</v>
       </c>
       <c r="G51" s="18" t="n">
         <f aca="false">PL!G83</f>
-        <v>52.7483150687281</v>
+        <v>50.80984888081</v>
       </c>
       <c r="H51" s="18" t="n">
         <f aca="false">PL!H83</f>
-        <v>53.4844797392841</v>
+        <v>51.4457527543033</v>
       </c>
       <c r="I51" s="18" t="n">
         <f aca="false">PL!I83</f>
-        <v>53.3401581935269</v>
+        <v>51.2117608300135</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55807,23 +57968,23 @@
       </c>
       <c r="E55" s="18" t="n">
         <f aca="false">E50+E51+E52+E53-E54</f>
-        <v>75.3370057599922</v>
+        <v>73.6157273791179</v>
       </c>
       <c r="F55" s="18" t="n">
         <f aca="false">F50+F51+F52+F53-F54</f>
-        <v>75.0057594186531</v>
+        <v>73.089621924314</v>
       </c>
       <c r="G55" s="18" t="n">
         <f aca="false">G50+G51+G52+G53-G54</f>
-        <v>77.1582985473617</v>
+        <v>75.0803231323806</v>
       </c>
       <c r="H55" s="18" t="n">
         <f aca="false">H50+H51+H52+H53-H54</f>
-        <v>80.7959423897917</v>
+        <v>78.5583319255045</v>
       </c>
       <c r="I55" s="18" t="n">
         <f aca="false">I50+I51+I52+I53-I54</f>
-        <v>98.4905067967244</v>
+        <v>96.099290429369</v>
       </c>
       <c r="J55" s="8" t="s">
         <v>707</v>
@@ -55949,23 +58110,23 @@
       </c>
       <c r="E59" s="18" t="n">
         <f aca="false">E55-E58</f>
-        <v>-11.0605202280501</v>
+        <v>-12.7817986089244</v>
       </c>
       <c r="F59" s="18" t="n">
         <f aca="false">F55-F58</f>
-        <v>38.1549631934909</v>
+        <v>36.2388256991519</v>
       </c>
       <c r="G59" s="18" t="n">
         <f aca="false">G55-G58</f>
-        <v>61.6238304344554</v>
+        <v>59.5458550194743</v>
       </c>
       <c r="H59" s="18" t="n">
         <f aca="false">H55-H58</f>
-        <v>64.9523725496627</v>
+        <v>62.7147620853756</v>
       </c>
       <c r="I59" s="18" t="n">
         <f aca="false">I55-I58</f>
-        <v>39.358488405686</v>
+        <v>36.9672720383306</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56021,23 +58182,23 @@
       </c>
       <c r="E61" s="18" t="n">
         <f aca="false">E59-E60</f>
-        <v>-17.4329922280501</v>
+        <v>-19.1542706089244</v>
       </c>
       <c r="F61" s="18" t="n">
         <f aca="false">F59-F60</f>
-        <v>31.8634911934909</v>
+        <v>29.9473536991519</v>
       </c>
       <c r="G61" s="18" t="n">
         <f aca="false">G59-G60</f>
-        <v>55.5138824344554</v>
+        <v>53.4359070194743</v>
       </c>
       <c r="H61" s="18" t="n">
         <f aca="false">H59-H60</f>
-        <v>58.8424245496627</v>
+        <v>56.6048140853756</v>
       </c>
       <c r="I61" s="18" t="n">
         <f aca="false">I59-I60</f>
-        <v>33.248540405686</v>
+        <v>30.8573240383306</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56087,15 +58248,15 @@
       </c>
       <c r="G63" s="18" t="n">
         <f aca="false">F72</f>
-        <v>41.8634911934909</v>
+        <v>39.9473536991519</v>
       </c>
       <c r="H63" s="18" t="n">
         <f aca="false">G72</f>
-        <v>97.3773736279463</v>
+        <v>93.3832607186262</v>
       </c>
       <c r="I63" s="18" t="n">
         <f aca="false">H72</f>
-        <v>156.219798177609</v>
+        <v>149.988074804002</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56111,23 +58272,23 @@
       </c>
       <c r="E64" s="18" t="n">
         <f aca="false">E61</f>
-        <v>-17.4329922280501</v>
+        <v>-19.1542706089244</v>
       </c>
       <c r="F64" s="18" t="n">
         <f aca="false">F61</f>
-        <v>31.8634911934909</v>
+        <v>29.9473536991519</v>
       </c>
       <c r="G64" s="18" t="n">
         <f aca="false">G61</f>
-        <v>55.5138824344554</v>
+        <v>53.4359070194743</v>
       </c>
       <c r="H64" s="18" t="n">
         <f aca="false">H61</f>
-        <v>58.8424245496627</v>
+        <v>56.6048140853756</v>
       </c>
       <c r="I64" s="18" t="n">
         <f aca="false">I61</f>
-        <v>33.248540405686</v>
+        <v>30.8573240383306</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56143,7 +58304,7 @@
       </c>
       <c r="E65" s="18" t="n">
         <f aca="false">MAX(0,-(E64+E63-min_cash))</f>
-        <v>14.1805691634164</v>
+        <v>15.9018475442907</v>
       </c>
       <c r="F65" s="18" t="n">
         <f aca="false">MAX(0,-(F64+F63-min_cash))</f>
@@ -56175,23 +58336,23 @@
       </c>
       <c r="E66" s="18" t="n">
         <f aca="false">PL!E85+Thesis!F57+rent_on</f>
-        <v>78.1474737344653</v>
+        <v>76.426195353591</v>
       </c>
       <c r="F66" s="18" t="n">
         <f aca="false">PL!F85+Thesis!G57+rent_on</f>
-        <v>101.824367078946</v>
+        <v>99.9929887746376</v>
       </c>
       <c r="G66" s="18" t="n">
         <f aca="false">PL!G85+Thesis!H57+rent_on</f>
-        <v>112.894225972762</v>
+        <v>110.955759784844</v>
       </c>
       <c r="H66" s="18" t="n">
         <f aca="false">PL!H85+Thesis!I57+rent_on</f>
-        <v>115.487832496643</v>
+        <v>113.449105511663</v>
       </c>
       <c r="I66" s="18" t="n">
         <f aca="false">PL!I85+Thesis!J57+rent_on</f>
-        <v>119.543734050579</v>
+        <v>117.415336687066</v>
       </c>
       <c r="J66" s="8" t="s">
         <v>720</v>
@@ -56245,23 +58406,23 @@
       </c>
       <c r="E68" s="18" t="n">
         <f aca="false">MAX(0,lev_max*E66/E62-E67-(debt_q1+D73))</f>
-        <v>67.4270859146618</v>
+        <v>59.6813332007271</v>
       </c>
       <c r="F68" s="18" t="n">
         <f aca="false">MAX(0,lev_max*F66/F62-F67-(debt_q1+E73))</f>
-        <v>93.8322248640166</v>
+        <v>83.8697441137561</v>
       </c>
       <c r="G68" s="18" t="n">
         <f aca="false">MAX(0,lev_max*G66/G62-G67-(debt_q1+F73))</f>
-        <v>143.646589886192</v>
+        <v>133.202213659687</v>
       </c>
       <c r="H68" s="18" t="n">
         <f aca="false">MAX(0,lev_max*H66/H62-H67-(debt_q1+G73))</f>
-        <v>155.317819243657</v>
+        <v>144.422269430369</v>
       </c>
       <c r="I68" s="18" t="n">
         <f aca="false">MAX(0,lev_max*I66/I62-I67-(debt_q1+H73))</f>
-        <v>173.569376236369</v>
+        <v>162.270309719684</v>
       </c>
       <c r="J68" s="8" t="s">
         <v>724</v>
@@ -56280,7 +58441,7 @@
       </c>
       <c r="E69" s="18" t="n">
         <f aca="false">MIN(E65,E68)</f>
-        <v>14.1805691634164</v>
+        <v>15.9018475442907</v>
       </c>
       <c r="F69" s="18" t="n">
         <f aca="false">MIN(F65,F68)</f>
@@ -56380,19 +58541,19 @@
       </c>
       <c r="F72" s="18" t="n">
         <f aca="false">F63+F64+F69+F70+F71</f>
-        <v>41.8634911934909</v>
+        <v>39.9473536991519</v>
       </c>
       <c r="G72" s="18" t="n">
         <f aca="false">G63+G64+G69+G70+G71</f>
-        <v>97.3773736279463</v>
+        <v>93.3832607186262</v>
       </c>
       <c r="H72" s="18" t="n">
         <f aca="false">H63+H64+H69+H70+H71</f>
-        <v>156.219798177609</v>
+        <v>149.988074804002</v>
       </c>
       <c r="I72" s="18" t="n">
         <f aca="false">I63+I64+I69+I70+I71</f>
-        <v>189.468338583295</v>
+        <v>180.845398842332</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56408,23 +58569,23 @@
       </c>
       <c r="E73" s="18" t="n">
         <f aca="false">D73+E69</f>
-        <v>14.1805691634164</v>
+        <v>15.9018475442907</v>
       </c>
       <c r="F73" s="18" t="n">
         <f aca="false">E73+F69</f>
-        <v>14.1805691634164</v>
+        <v>15.9018475442907</v>
       </c>
       <c r="G73" s="18" t="n">
         <f aca="false">F73+G69</f>
-        <v>14.1805691634164</v>
+        <v>15.9018475442907</v>
       </c>
       <c r="H73" s="18" t="n">
         <f aca="false">G73+H69</f>
-        <v>14.1805691634164</v>
+        <v>15.9018475442907</v>
       </c>
       <c r="I73" s="18" t="n">
         <f aca="false">H73+I69</f>
-        <v>14.1805691634164</v>
+        <v>15.9018475442907</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56472,23 +58633,23 @@
       </c>
       <c r="E75" s="18" t="n">
         <f aca="false">debt_q1+E73+E74</f>
-        <v>139.180569163416</v>
+        <v>140.901847544291</v>
       </c>
       <c r="F75" s="18" t="n">
         <f aca="false">debt_q1+F73+F74</f>
-        <v>139.180569163416</v>
+        <v>140.901847544291</v>
       </c>
       <c r="G75" s="18" t="n">
         <f aca="false">debt_q1+G73+G74</f>
-        <v>139.180569163416</v>
+        <v>140.901847544291</v>
       </c>
       <c r="H75" s="18" t="n">
         <f aca="false">debt_q1+H73+H74</f>
-        <v>139.180569163416</v>
+        <v>140.901847544291</v>
       </c>
       <c r="I75" s="18" t="n">
         <f aca="false">debt_q1+I73+I74</f>
-        <v>139.180569163416</v>
+        <v>140.901847544291</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56504,23 +58665,23 @@
       </c>
       <c r="E76" s="19" t="n">
         <f aca="false">(E75+E67)/(E66/E62)</f>
-        <v>3.81864058802246</v>
+        <v>3.92716649109788</v>
       </c>
       <c r="F76" s="19" t="n">
         <f aca="false">(F75+F67)/(F66/F62)</f>
-        <v>3.57848948580974</v>
+        <v>3.66124375177163</v>
       </c>
       <c r="G76" s="19" t="n">
         <f aca="false">(G75+G67)/(G66/G62)</f>
-        <v>3.22760020587015</v>
+        <v>3.29950158587548</v>
       </c>
       <c r="H76" s="19" t="n">
         <f aca="false">(H75+H67)/(H66/H62)</f>
-        <v>3.15511529755162</v>
+        <v>3.22698626596468</v>
       </c>
       <c r="I76" s="19" t="n">
         <f aca="false">(I75+I67)/(I66/I62)</f>
-        <v>3.04806797181916</v>
+        <v>3.11798028862137</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56674,19 +58835,19 @@
       </c>
       <c r="F81" s="18" t="n">
         <f aca="false">r_old*debt_q1+r_new*E73+r_junk*E74</f>
-        <v>6.53447301147815</v>
+        <v>6.63430715756886</v>
       </c>
       <c r="G81" s="18" t="n">
         <f aca="false">r_old*debt_q1+r_new*F73+r_junk*F74</f>
-        <v>6.53447301147815</v>
+        <v>6.63430715756886</v>
       </c>
       <c r="H81" s="18" t="n">
         <f aca="false">r_old*debt_q1+r_new*G73+r_junk*G74</f>
-        <v>6.53447301147815</v>
+        <v>6.63430715756886</v>
       </c>
       <c r="I81" s="18" t="n">
         <f aca="false">r_old*debt_q1+r_new*H73+r_junk*H74</f>
-        <v>6.53447301147815</v>
+        <v>6.63430715756886</v>
       </c>
       <c r="J81" s="8" t="s">
         <v>739</v>
@@ -56713,15 +58874,15 @@
       </c>
       <c r="G82" s="18" t="n">
         <f aca="false">r_cash*G63</f>
-        <v>1.40891729827141</v>
+        <v>1.34442962214419</v>
       </c>
       <c r="H82" s="18" t="n">
         <f aca="false">r_cash*H63</f>
-        <v>3.27723900356365</v>
+        <v>3.14281699028289</v>
       </c>
       <c r="I82" s="18" t="n">
         <f aca="false">r_cash*I63</f>
-        <v>5.25758291317863</v>
+        <v>5.04785403943188</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56750,19 +58911,19 @@
       </c>
       <c r="F85" s="18" t="n">
         <f aca="false">PL!F117</f>
-        <v>3.6907195283932</v>
+        <v>3.64153722525802</v>
       </c>
       <c r="G85" s="18" t="n">
         <f aca="false">PL!G117</f>
-        <v>7.42747293327942</v>
+        <v>7.32455713596512</v>
       </c>
       <c r="H85" s="18" t="n">
         <f aca="false">PL!H117</f>
-        <v>15.0260087016643</v>
+        <v>14.864764240766</v>
       </c>
       <c r="I85" s="18" t="n">
         <f aca="false">PL!I117</f>
-        <v>19.7455346451292</v>
+        <v>19.5214301240907</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56782,23 +58943,23 @@
       </c>
       <c r="E86" s="18" t="n">
         <f aca="false">PL!E123</f>
-        <v>36.7195841621974</v>
+        <v>34.9983057813231</v>
       </c>
       <c r="F86" s="18" t="n">
         <f aca="false">PL!F123</f>
-        <v>43.1686790926506</v>
+        <v>41.3373007883426</v>
       </c>
       <c r="G86" s="18" t="n">
         <f aca="false">PL!G123</f>
-        <v>48.2693132537281</v>
+        <v>46.33084706581</v>
       </c>
       <c r="H86" s="18" t="n">
         <f aca="false">PL!H123</f>
-        <v>51.0230845542841</v>
+        <v>48.9843575693033</v>
       </c>
       <c r="I86" s="18" t="n">
         <f aca="false">PL!I123</f>
-        <v>50.8787630085269</v>
+        <v>48.7503656450135</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56924,23 +59085,23 @@
       </c>
       <c r="E90" s="18" t="n">
         <f aca="false">E85+E86+E87+E88-E89</f>
-        <v>48.839287121429</v>
+        <v>47.1180087405547</v>
       </c>
       <c r="F90" s="18" t="n">
         <f aca="false">F85+F86+F87+F88-F89</f>
-        <v>52.9815540755402</v>
+        <v>51.1009934680969</v>
       </c>
       <c r="G90" s="18" t="n">
         <f aca="false">G85+G86+G87+G88-G89</f>
-        <v>59.2942948877998</v>
+        <v>57.2529129025675</v>
       </c>
       <c r="H90" s="18" t="n">
         <f aca="false">H85+H86+H87+H88-H89</f>
-        <v>62.3248987476528</v>
+        <v>60.1249273017737</v>
       </c>
       <c r="I90" s="18" t="n">
         <f aca="false">I85+I86+I87+I88-I89</f>
-        <v>79.4916877071477</v>
+        <v>77.1391858225957</v>
       </c>
       <c r="J90" s="8" t="s">
         <v>707</v>
@@ -57066,23 +59227,23 @@
       </c>
       <c r="E94" s="18" t="n">
         <f aca="false">E90-E93</f>
-        <v>7.6847155333867</v>
+        <v>5.96343715251236</v>
       </c>
       <c r="F94" s="18" t="n">
         <f aca="false">F90-F93</f>
-        <v>9.86745412037803</v>
+        <v>7.9868935129348</v>
       </c>
       <c r="G94" s="18" t="n">
         <f aca="false">G90-G93</f>
-        <v>19.5485472148936</v>
+        <v>17.5071652296612</v>
       </c>
       <c r="H94" s="18" t="n">
         <f aca="false">H90-H93</f>
-        <v>46.4813289075238</v>
+        <v>44.2813574616447</v>
       </c>
       <c r="I94" s="18" t="n">
         <f aca="false">I90-I93</f>
-        <v>20.3596693161093</v>
+        <v>18.0071674315573</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57138,23 +59299,23 @@
       </c>
       <c r="E96" s="18" t="n">
         <f aca="false">E94-E95</f>
-        <v>1.3122435333867</v>
+        <v>-0.409034847487638</v>
       </c>
       <c r="F96" s="18" t="n">
         <f aca="false">F94-F95</f>
-        <v>3.57598212037803</v>
+        <v>1.6954215129348</v>
       </c>
       <c r="G96" s="18" t="n">
         <f aca="false">G94-G95</f>
-        <v>13.4385992148936</v>
+        <v>11.3972172296612</v>
       </c>
       <c r="H96" s="18" t="n">
         <f aca="false">H94-H95</f>
-        <v>40.3713809075238</v>
+        <v>38.1714094616447</v>
       </c>
       <c r="I96" s="18" t="n">
         <f aca="false">I94-I95</f>
-        <v>14.2497213161093</v>
+        <v>11.8972194315573</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57200,19 +59361,19 @@
       </c>
       <c r="F98" s="18" t="n">
         <f aca="false">E107</f>
-        <v>12.015104485817</v>
+        <v>10.2938261049427</v>
       </c>
       <c r="G98" s="18" t="n">
         <f aca="false">F107</f>
-        <v>15.5910866061951</v>
+        <v>11.9892476178775</v>
       </c>
       <c r="H98" s="18" t="n">
         <f aca="false">G107</f>
-        <v>29.0296858210886</v>
+        <v>23.3864648475387</v>
       </c>
       <c r="I98" s="18" t="n">
         <f aca="false">H107</f>
-        <v>69.4010667286124</v>
+        <v>61.5578743091834</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57228,23 +59389,23 @@
       </c>
       <c r="E99" s="18" t="n">
         <f aca="false">E96</f>
-        <v>1.3122435333867</v>
+        <v>-0.409034847487638</v>
       </c>
       <c r="F99" s="18" t="n">
         <f aca="false">F96</f>
-        <v>3.57598212037803</v>
+        <v>1.6954215129348</v>
       </c>
       <c r="G99" s="18" t="n">
         <f aca="false">G96</f>
-        <v>13.4385992148936</v>
+        <v>11.3972172296612</v>
       </c>
       <c r="H99" s="18" t="n">
         <f aca="false">H96</f>
-        <v>40.3713809075238</v>
+        <v>38.1714094616447</v>
       </c>
       <c r="I99" s="18" t="n">
         <f aca="false">I96</f>
-        <v>14.2497213161093</v>
+        <v>11.8972194315573</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57292,23 +59453,23 @@
       </c>
       <c r="E101" s="18" t="n">
         <f aca="false">PL!E125+Thesis!F92+rent_on</f>
-        <v>60.6427333515996</v>
+        <v>58.9214549707253</v>
       </c>
       <c r="F101" s="18" t="n">
         <f aca="false">PL!F125+Thesis!G92+rent_on</f>
-        <v>71.8584636165349</v>
+        <v>70.0270853122269</v>
       </c>
       <c r="G101" s="18" t="n">
         <f aca="false">PL!G125+Thesis!H92+rent_on</f>
-        <v>83.5502669440579</v>
+        <v>81.6118007561398</v>
       </c>
       <c r="H101" s="18" t="n">
         <f aca="false">PL!H125+Thesis!I92+rent_on</f>
-        <v>94.8017449430326</v>
+        <v>92.7630179580518</v>
       </c>
       <c r="I101" s="18" t="n">
         <f aca="false">PL!I125+Thesis!J92+rent_on</f>
-        <v>98.8576464969686</v>
+        <v>96.7292491334552</v>
       </c>
       <c r="J101" s="8" t="s">
         <v>720</v>
@@ -57370,15 +59531,15 @@
       </c>
       <c r="G103" s="18" t="n">
         <f aca="false">MAX(0,lev_max*G101/G97-G102-(debt_q1+F108))</f>
-        <v>25.7793434204383</v>
+        <v>17.0562455748071</v>
       </c>
       <c r="H103" s="18" t="n">
         <f aca="false">MAX(0,lev_max*H101/H97-H102-(debt_q1+G108))</f>
-        <v>76.4109944158243</v>
+        <v>67.2367229834107</v>
       </c>
       <c r="I103" s="18" t="n">
         <f aca="false">MAX(0,lev_max*I101/I97-I102-(debt_q1+H108))</f>
-        <v>94.6625514085363</v>
+        <v>85.0847632727261</v>
       </c>
       <c r="J103" s="8" t="s">
         <v>724</v>
@@ -57493,23 +59654,23 @@
       </c>
       <c r="E107" s="18" t="n">
         <f aca="false">E98+E99+E104+E105+E106</f>
-        <v>12.015104485817</v>
+        <v>10.2938261049427</v>
       </c>
       <c r="F107" s="18" t="n">
         <f aca="false">F98+F99+F104+F105+F106</f>
-        <v>15.5910866061951</v>
+        <v>11.9892476178775</v>
       </c>
       <c r="G107" s="18" t="n">
         <f aca="false">G98+G99+G104+G105+G106</f>
-        <v>29.0296858210886</v>
+        <v>23.3864648475387</v>
       </c>
       <c r="H107" s="18" t="n">
         <f aca="false">H98+H99+H104+H105+H106</f>
-        <v>69.4010667286124</v>
+        <v>61.5578743091834</v>
       </c>
       <c r="I107" s="18" t="n">
         <f aca="false">I98+I99+I104+I105+I106</f>
-        <v>83.6507880447217</v>
+        <v>73.4550937407407</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57621,23 +59782,23 @@
       </c>
       <c r="E111" s="19" t="n">
         <f aca="false">(E110+E102)/(E101/E97)</f>
-        <v>4.68706686162151</v>
+        <v>4.82399061651912</v>
       </c>
       <c r="F111" s="19" t="n">
         <f aca="false">(F110+F102)/(F101/F97)</f>
-        <v>4.87342534480852</v>
+        <v>5.00087725008708</v>
       </c>
       <c r="G111" s="19" t="n">
         <f aca="false">(G110+G102)/(G101/G97)</f>
-        <v>4.19145109449262</v>
+        <v>4.29100760653754</v>
       </c>
       <c r="H111" s="19" t="n">
         <f aca="false">(H110+H102)/(H101/H97)</f>
-        <v>3.69399168800384</v>
+        <v>3.77517749569321</v>
       </c>
       <c r="I111" s="19" t="n">
         <f aca="false">(I110+I102)/(I101/I97)</f>
-        <v>3.54243571678151</v>
+        <v>3.62038226250122</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57826,19 +59987,19 @@
       </c>
       <c r="F117" s="18" t="n">
         <f aca="false">r_cash*F98</f>
-        <v>0.404368772598643</v>
+        <v>0.346439086927049</v>
       </c>
       <c r="G117" s="18" t="n">
         <f aca="false">r_cash*G98</f>
-        <v>0.524718579174098</v>
+        <v>0.403498558780336</v>
       </c>
       <c r="H117" s="18" t="n">
         <f aca="false">r_cash*H98</f>
-        <v>0.976995117957945</v>
+        <v>0.787072313601897</v>
       </c>
       <c r="I117" s="18" t="n">
         <f aca="false">r_cash*I98</f>
-        <v>2.33569539101492</v>
+        <v>2.07173246870798</v>
       </c>
     </row>
   </sheetData>
@@ -58062,15 +60223,15 @@
       </c>
       <c r="C17" s="22" t="n">
         <f aca="false">PL!E30*(1-etr)+PL!E43-CF!E23+CF!E18-CF!E19</f>
-        <v>-1.96423784994101</v>
+        <v>-3.68551623081535</v>
       </c>
       <c r="D17" s="22" t="n">
         <f aca="false">PL!E70*(1-etr)+PL!E83-CF!E58+CF!E53-CF!E54</f>
-        <v>-11.2780153749778</v>
+        <v>-12.9992937558521</v>
       </c>
       <c r="E17" s="22" t="n">
         <f aca="false">PL!E110*(1-etr)+PL!E123-CF!E93+CF!E88-CF!E89</f>
-        <v>7.54006934456923</v>
+        <v>5.81879096369489</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58082,15 +60243,15 @@
       </c>
       <c r="C18" s="22" t="n">
         <f aca="false">PL!F30*(1-etr)+PL!F43-CF!F23+CF!F18-CF!F19</f>
-        <v>59.5258898978923</v>
+        <v>57.6945115935842</v>
       </c>
       <c r="D18" s="22" t="n">
         <f aca="false">PL!F70*(1-etr)+PL!F83-CF!F58+CF!F53-CF!F54</f>
-        <v>38.5411467255959</v>
+        <v>36.7097684212879</v>
       </c>
       <c r="E18" s="22" t="n">
         <f aca="false">PL!F110*(1-etr)+PL!F123-CF!F93+CF!F88-CF!F89</f>
-        <v>9.49778023244178</v>
+        <v>7.66640192813373</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58102,15 +60263,15 @@
       </c>
       <c r="C19" s="22" t="n">
         <f aca="false">PL!G30*(1-etr)+PL!G43-CF!G23+CF!G18-CF!G19</f>
-        <v>60.803460333745</v>
+        <v>58.864994145827</v>
       </c>
       <c r="D19" s="22" t="n">
         <f aca="false">PL!G70*(1-etr)+PL!G83-CF!G58+CF!G53-CF!G54</f>
-        <v>60.9045403229679</v>
+        <v>58.9660741350499</v>
       </c>
       <c r="E19" s="22" t="n">
         <f aca="false">PL!G110*(1-etr)+PL!G123-CF!G93+CF!G88-CF!G89</f>
-        <v>18.8816622291748</v>
+        <v>16.9431960412567</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58122,15 +60283,15 @@
       </c>
       <c r="C20" s="22" t="n">
         <f aca="false">PL!H30*(1-etr)+PL!H43-CF!H23+CF!H18-CF!H19</f>
-        <v>62.3429618446793</v>
+        <v>60.3042348596985</v>
       </c>
       <c r="D20" s="22" t="n">
         <f aca="false">PL!H70*(1-etr)+PL!H83-CF!H58+CF!H53-CF!H54</f>
-        <v>62.4440418339021</v>
+        <v>60.4053148489213</v>
       </c>
       <c r="E20" s="22" t="n">
         <f aca="false">PL!H110*(1-etr)+PL!H123-CF!H93+CF!H88-CF!H89</f>
-        <v>45.2276256638975</v>
+        <v>43.1888986789167</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58142,15 +60303,15 @@
       </c>
       <c r="C21" s="22" t="n">
         <f aca="false">PL!I30*(1-etr)+PL!I43-CF!I23+CF!I18-CF!I19</f>
-        <v>34.8568168259002</v>
+        <v>32.7284194623868</v>
       </c>
       <c r="D21" s="22" t="n">
         <f aca="false">PL!I70*(1-etr)+PL!I83-CF!I58+CF!I53-CF!I54</f>
-        <v>34.9578968151231</v>
+        <v>32.8294994516097</v>
       </c>
       <c r="E21" s="22" t="n">
         <f aca="false">PL!I110*(1-etr)+PL!I123-CF!I93+CF!I88-CF!I89</f>
-        <v>17.7414806451184</v>
+        <v>15.613083281605</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58159,15 +60320,15 @@
       </c>
       <c r="C22" s="22" t="n">
         <f aca="false">PL!I30*(1-etr)+PL!I43-CF!I22-Thesis!J6*cx_vr200/life_ai/1000</f>
-        <v>28.7262262733738</v>
+        <v>26.5978289098604</v>
       </c>
       <c r="D22" s="22" t="n">
         <f aca="false">PL!I70*(1-etr)+PL!I83-CF!I57-Thesis!J41*cx_vr200/life_ai/1000</f>
-        <v>29.8742360415967</v>
+        <v>27.7458386780833</v>
       </c>
       <c r="E22" s="22" t="n">
         <f aca="false">PL!I110*(1-etr)+PL!I123-CF!I92-Thesis!J76*cx_vr200/life_ai/1000</f>
-        <v>27.5634906356461</v>
+        <v>25.4350932721327</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>762</v>
@@ -58182,15 +60343,15 @@
       </c>
       <c r="C23" s="23" t="n">
         <f aca="false">C22*(1+tp_g)/(wacc-tp_g)</f>
-        <v>320.89573152967</v>
+        <v>297.119770759511</v>
       </c>
       <c r="D23" s="23" t="n">
         <f aca="false">D22*(1+tp_g)/(wacc-tp_g)</f>
-        <v>333.719951142482</v>
+        <v>309.943990372323</v>
       </c>
       <c r="E23" s="23" t="n">
         <f aca="false">E22*(1+tp_g)/(wacc-tp_g)</f>
-        <v>307.907011762113</v>
+        <v>284.131050991954</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58199,15 +60360,15 @@
       </c>
       <c r="C24" s="23" t="n">
         <f aca="false">C16/(1+wacc)^$B$16+C17/(1+wacc)^$B$17+C18/(1+wacc)^$B$18+C19/(1+wacc)^$B$19+C20/(1+wacc)^$B$20+C21/(1+wacc)^$B$21+C23/(1+wacc)^$B$23</f>
-        <v>293.984708009075</v>
+        <v>275.085486918732</v>
       </c>
       <c r="D24" s="23" t="n">
         <f aca="false">D16/(1+wacc)^$B$16+D17/(1+wacc)^$B$17+D18/(1+wacc)^$B$18+D19/(1+wacc)^$B$19+D20/(1+wacc)^$B$20+D21/(1+wacc)^$B$21+D23/(1+wacc)^$B$23</f>
-        <v>272.402063327711</v>
+        <v>253.502842237368</v>
       </c>
       <c r="E24" s="23" t="n">
         <f aca="false">E16/(1+wacc)^$B$16+E17/(1+wacc)^$B$17+E18/(1+wacc)^$B$18+E19/(1+wacc)^$B$19+E20/(1+wacc)^$B$20+E21/(1+wacc)^$B$21+E23/(1+wacc)^$B$23</f>
-        <v>201.707416820355</v>
+        <v>182.808195730013</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58216,15 +60377,15 @@
       </c>
       <c r="C25" s="12" t="n">
         <f aca="false">C23/(1+wacc)^$B$23/C24</f>
-        <v>0.562503574578166</v>
+        <v>0.55660866126205</v>
       </c>
       <c r="D25" s="12" t="n">
         <f aca="false">D23/(1+wacc)^$B$23/D24</f>
-        <v>0.631332091179422</v>
+        <v>0.6300666231298</v>
       </c>
       <c r="E25" s="12" t="n">
         <f aca="false">E23/(1+wacc)^$B$23/E24</f>
-        <v>0.786654077862035</v>
+        <v>0.80095685465344</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58233,15 +60394,15 @@
       </c>
       <c r="C26" s="23" t="n">
         <f aca="false">C24-netdebt0</f>
-        <v>206.061708009075</v>
+        <v>187.162486918732</v>
       </c>
       <c r="D26" s="23" t="n">
         <f aca="false">D24-netdebt0</f>
-        <v>184.479063327711</v>
+        <v>165.579842237368</v>
       </c>
       <c r="E26" s="23" t="n">
         <f aca="false">E24-netdebt0</f>
-        <v>113.784416820355</v>
+        <v>94.885195730013</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58250,15 +60411,15 @@
       </c>
       <c r="C27" s="22" t="n">
         <f aca="false">MAX(0,C26/shfd)</f>
-        <v>66.708786803992</v>
+        <v>60.590502515959</v>
       </c>
       <c r="D27" s="22" t="n">
         <f aca="false">MAX(0,D26/shfd)</f>
-        <v>59.7217921962796</v>
+        <v>53.6035079082467</v>
       </c>
       <c r="E27" s="22" t="n">
         <f aca="false">MAX(0,E26/shfd)</f>
-        <v>36.8356667360604</v>
+        <v>30.7173824480274</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58267,15 +60428,15 @@
       </c>
       <c r="C28" s="26" t="n">
         <f aca="false">MAX(0,C27*(1+ke)^t_tp-dps_q*4*t_tp)</f>
-        <v>75.369826887532</v>
+        <v>68.2431791536029</v>
       </c>
       <c r="D28" s="26" t="n">
         <f aca="false">MAX(0,D27*(1+ke)^t_tp-dps_q*4*t_tp)</f>
-        <v>67.2312954065051</v>
+        <v>60.104647672576</v>
       </c>
       <c r="E28" s="26" t="n">
         <f aca="false">MAX(0,E27*(1+ke)^t_tp-dps_q*4*t_tp)</f>
-        <v>40.5732738973533</v>
+        <v>33.4466261634242</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58497,15 +60658,15 @@
       </c>
       <c r="C45" s="22" t="n">
         <f aca="false">PL!F46-Thesis!G28</f>
-        <v>38.7567713964115</v>
+        <v>36.9253930921035</v>
       </c>
       <c r="D45" s="22" t="n">
         <f aca="false">PL!F86-Thesis!G63</f>
-        <v>38.7567713964115</v>
+        <v>36.9253930921035</v>
       </c>
       <c r="E45" s="22" t="n">
         <f aca="false">PL!F126-Thesis!G98</f>
-        <v>38.7567713964115</v>
+        <v>36.9253930921035</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>804</v>
@@ -58540,15 +60701,15 @@
       </c>
       <c r="C47" s="23" t="n">
         <f aca="false">C45*mult_sw*mult_adj</f>
-        <v>582.126706374101</v>
+        <v>554.619404243394</v>
       </c>
       <c r="D47" s="23" t="n">
         <f aca="false">D45*mult_sw*mult_adj</f>
-        <v>582.126706374101</v>
+        <v>554.619404243394</v>
       </c>
       <c r="E47" s="23" t="n">
         <f aca="false">E45*mult_sw*mult_adj</f>
-        <v>582.126706374101</v>
+        <v>554.619404243394</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58560,15 +60721,15 @@
       </c>
       <c r="C48" s="23" t="n">
         <f aca="false">C46+C47</f>
-        <v>930.24585515039</v>
+        <v>902.738553019684</v>
       </c>
       <c r="D48" s="23" t="n">
         <f aca="false">D46+D47</f>
-        <v>892.383615138639</v>
+        <v>864.876313007932</v>
       </c>
       <c r="E48" s="23" t="n">
         <f aca="false">E46+E47</f>
-        <v>702.291066414315</v>
+        <v>674.783764283608</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58580,15 +60741,15 @@
       </c>
       <c r="C49" s="23" t="n">
         <f aca="false">CF!E40-CF!E37</f>
-        <v>115.437084051658</v>
+        <v>117.158362432533</v>
       </c>
       <c r="D49" s="23" t="n">
         <f aca="false">CF!E75-CF!E72</f>
-        <v>129.180569163416</v>
+        <v>130.901847544291</v>
       </c>
       <c r="E49" s="23" t="n">
         <f aca="false">CF!E110-CF!E107</f>
-        <v>112.984895514183</v>
+        <v>114.706173895057</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58620,15 +60781,15 @@
       </c>
       <c r="C51" s="22" t="n">
         <f aca="false">MAX(0,(C48-C49)/C50)</f>
-        <v>263.779744050527</v>
+        <v>254.317514678709</v>
       </c>
       <c r="D51" s="22" t="n">
         <f aca="false">MAX(0,(D48-D49)/D50)</f>
-        <v>247.073314950279</v>
+        <v>237.611085578461</v>
       </c>
       <c r="E51" s="22" t="n">
         <f aca="false">MAX(0,(E48-E49)/E50)</f>
-        <v>190.777316643045</v>
+        <v>181.315087271227</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58640,15 +60801,15 @@
       </c>
       <c r="C52" s="26" t="n">
         <f aca="false">C51/(1+ke)^(7/12)</f>
-        <v>244.406990108413</v>
+        <v>235.639694466339</v>
       </c>
       <c r="D52" s="26" t="n">
         <f aca="false">D51/(1+ke)^(7/12)</f>
-        <v>228.927529899864</v>
+        <v>220.160234257791</v>
       </c>
       <c r="E52" s="26" t="n">
         <f aca="false">E51/(1+ke)^(7/12)</f>
-        <v>176.766073943702</v>
+        <v>167.998778301628</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>812</v>
@@ -58663,15 +60824,15 @@
       </c>
       <c r="C53" s="12" t="n">
         <f aca="false">C46/C48</f>
-        <v>0.374222735687449</v>
+        <v>0.385625658294777</v>
       </c>
       <c r="D53" s="12" t="n">
         <f aca="false">D46/D48</f>
-        <v>0.347672126091577</v>
+        <v>0.358729802282945</v>
       </c>
       <c r="E53" s="12" t="n">
         <f aca="false">E46/E48</f>
-        <v>0.171103358403428</v>
+        <v>0.17807832138313</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58708,15 +60869,15 @@
       </c>
       <c r="C57" s="22" t="n">
         <f aca="false">w_dcf*C28+(1-w_dcf)*C52</f>
-        <v>159.888408497972</v>
+        <v>151.941436809971</v>
       </c>
       <c r="D57" s="22" t="n">
         <f aca="false">w_dcf*D28+(1-w_dcf)*D52</f>
-        <v>148.079412653185</v>
+        <v>140.132440965183</v>
       </c>
       <c r="E57" s="22" t="n">
         <f aca="false">w_dcf*E28+(1-w_dcf)*E52</f>
-        <v>108.669673920527</v>
+        <v>100.722702232526</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58748,7 +60909,7 @@
       </c>
       <c r="C59" s="22" t="n">
         <f aca="false">wA*C28+wB*D28+wC*E28</f>
-        <v>62.6014228994739</v>
+        <v>55.4747751655448</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58760,7 +60921,7 @@
       </c>
       <c r="C60" s="22" t="n">
         <f aca="false">wA*C52+wB*D52+wC*E52</f>
-        <v>219.75703096296</v>
+        <v>210.989735320887</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>819</v>
@@ -58775,7 +60936,7 @@
       </c>
       <c r="C61" s="26" t="n">
         <f aca="false">w_dcf*C59+(1-w_dcf)*C60</f>
-        <v>141.179226931217</v>
+        <v>133.232255243216</v>
       </c>
       <c r="D61" s="13"/>
       <c r="E61" s="13"/>
@@ -58820,7 +60981,7 @@
       </c>
       <c r="C64" s="28" t="n">
         <f aca="false">C61/px-1</f>
-        <v>0.11993675179452</v>
+        <v>0.0568955675330478</v>
       </c>
       <c r="D64" s="13"/>
       <c r="E64" s="13"/>
@@ -58835,7 +60996,7 @@
       </c>
       <c r="C65" s="12" t="n">
         <f aca="false">C60/px-1</f>
-        <v>0.743273290202764</v>
+        <v>0.673724697135389</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58876,11 +61037,11 @@
       </c>
       <c r="C68" s="22" t="n">
         <f aca="false">E28</f>
-        <v>40.5732738973533</v>
+        <v>33.4466261634242</v>
       </c>
       <c r="D68" s="22" t="n">
         <f aca="false">C28</f>
-        <v>75.369826887532</v>
+        <v>68.2431791536029</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>830</v>
@@ -58895,7 +61056,7 @@
       </c>
       <c r="C69" s="22" t="n">
         <f aca="false">E28</f>
-        <v>40.5732738973533</v>
+        <v>33.4466261634242</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58907,15 +61068,15 @@
       </c>
       <c r="C70" s="22" t="n">
         <f aca="false">C28</f>
-        <v>75.369826887532</v>
+        <v>68.2431791536029</v>
       </c>
       <c r="D70" s="22" t="n">
         <f aca="false">D28</f>
-        <v>67.2312954065051</v>
+        <v>60.104647672576</v>
       </c>
       <c r="E70" s="22" t="n">
         <f aca="false">E28</f>
-        <v>40.5732738973533</v>
+        <v>33.4466261634242</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58927,7 +61088,7 @@
       </c>
       <c r="C71" s="12" t="n">
         <f aca="false">C61/cons_tp-1</f>
-        <v>-0.405210537027228</v>
+        <v>-0.43869120642393</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58939,7 +61100,7 @@
       </c>
       <c r="C72" s="12" t="n">
         <f aca="false">D25</f>
-        <v>0.631332091179422</v>
+        <v>0.6300666231298</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59189,27 +61350,27 @@
       </c>
       <c r="C9" s="22" t="n">
         <f aca="false">PL!E46</f>
-        <v>80.7872608388298</v>
+        <v>79.0659824579554</v>
       </c>
       <c r="D9" s="12" t="n">
         <f aca="false">C9/B9-1</f>
-        <v>0.0823297987571308</v>
+        <v>0.0592693451134136</v>
       </c>
       <c r="E9" s="22" t="n">
         <f aca="false">PL!E86</f>
-        <v>69.9612054991712</v>
+        <v>68.2399271182969</v>
       </c>
       <c r="F9" s="12" t="n">
         <f aca="false">E9/B9-1</f>
-        <v>-0.0627099287375575</v>
+        <v>-0.0857703823812749</v>
       </c>
       <c r="G9" s="22" t="n">
         <f aca="false">PL!E126</f>
-        <v>52.4564651163055</v>
+        <v>50.7351867354311</v>
       </c>
       <c r="H9" s="12" t="n">
         <f aca="false">G9/B9-1</f>
-        <v>-0.297225890031008</v>
+        <v>-0.320286343674725</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>123</v>
@@ -59228,27 +61389,27 @@
       </c>
       <c r="C10" s="22" t="n">
         <f aca="false">PL!F46</f>
-        <v>93.6337504029646</v>
+        <v>91.8023720986566</v>
       </c>
       <c r="D10" s="12" t="n">
         <f aca="false">C10/B10-1</f>
-        <v>-0.129336633691039</v>
+        <v>-0.146365899234199</v>
       </c>
       <c r="E10" s="22" t="n">
         <f aca="false">PL!F86</f>
-        <v>87.6652038361649</v>
+        <v>85.8338255318568</v>
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">E10/B10-1</f>
-        <v>-0.184835797437631</v>
+        <v>-0.201865062980791</v>
       </c>
       <c r="G10" s="22" t="n">
         <f aca="false">PL!F126</f>
-        <v>57.6993003737542</v>
+        <v>55.8679220694462</v>
       </c>
       <c r="H10" s="12" t="n">
         <f aca="false">G10/B10-1</f>
-        <v>-0.463476931332079</v>
+        <v>-0.480506196875239</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>123</v>
@@ -59339,27 +61500,27 @@
       </c>
       <c r="C13" s="22" t="n">
         <f aca="false">PL!F41</f>
-        <v>9.58331719475045</v>
+        <v>9.55573847701983</v>
       </c>
       <c r="D13" s="12" t="n">
         <f aca="false">C13/B13-1</f>
-        <v>-0.286424631813071</v>
+        <v>-0.288478147653029</v>
       </c>
       <c r="E13" s="22" t="n">
         <f aca="false">PL!F81</f>
-        <v>7.21464485529205</v>
+        <v>7.18706613756142</v>
       </c>
       <c r="F13" s="12" t="n">
         <f aca="false">E13/B13-1</f>
-        <v>-0.462796362226951</v>
+        <v>-0.464849878066908</v>
       </c>
       <c r="G13" s="22" t="n">
         <f aca="false">PL!F121</f>
-        <v>1.12148434801486</v>
+        <v>1.10548154224228</v>
       </c>
       <c r="H13" s="12" t="n">
         <f aca="false">G13/B13-1</f>
-        <v>-0.916494091733816</v>
+        <v>-0.917685663273099</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>857</v>
@@ -59528,27 +61689,27 @@
       </c>
       <c r="C18" s="22" t="n">
         <f aca="false">CF!E24</f>
-        <v>-1.62368816511926</v>
+        <v>-3.3449665459936</v>
       </c>
       <c r="D18" s="22" t="n">
         <f aca="false">C18-B18</f>
-        <v>30.9363118348807</v>
+        <v>29.2150334540064</v>
       </c>
       <c r="E18" s="22" t="n">
         <f aca="false">CF!E59</f>
-        <v>-11.0605202280501</v>
+        <v>-12.7817986089244</v>
       </c>
       <c r="F18" s="22" t="n">
         <f aca="false">E18-B18</f>
-        <v>21.4994797719499</v>
+        <v>19.7782013910756</v>
       </c>
       <c r="G18" s="22" t="n">
         <f aca="false">CF!E94</f>
-        <v>7.6847155333867</v>
+        <v>5.96343715251236</v>
       </c>
       <c r="H18" s="22" t="n">
         <f aca="false">G18-B18</f>
-        <v>40.2447155333867</v>
+        <v>38.5234371525124</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>857</v>
@@ -59564,27 +61725,27 @@
       </c>
       <c r="C19" s="22" t="n">
         <f aca="false">CF!F24</f>
-        <v>59.8164630596604</v>
+        <v>57.9003255653214</v>
       </c>
       <c r="D19" s="22" t="n">
         <f aca="false">C19-B19</f>
-        <v>53.6624630596604</v>
+        <v>51.7463255653214</v>
       </c>
       <c r="E19" s="22" t="n">
         <f aca="false">CF!F59</f>
-        <v>38.1549631934909</v>
+        <v>36.2388256991519</v>
       </c>
       <c r="F19" s="22" t="n">
         <f aca="false">E19-B19</f>
-        <v>32.0009631934909</v>
+        <v>30.0848256991519</v>
       </c>
       <c r="G19" s="22" t="n">
         <f aca="false">CF!F94</f>
-        <v>9.86745412037803</v>
+        <v>7.9868935129348</v>
       </c>
       <c r="H19" s="22" t="n">
         <f aca="false">G19-B19</f>
-        <v>3.71345412037803</v>
+        <v>1.8328935129348</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>857</v>
@@ -60219,15 +62380,15 @@
       </c>
       <c r="C42" s="22" t="n">
         <f aca="false">Val!C57</f>
-        <v>159.888408497972</v>
+        <v>151.941436809971</v>
       </c>
       <c r="E42" s="22" t="n">
         <f aca="false">Val!D57</f>
-        <v>148.079412653185</v>
+        <v>140.132440965183</v>
       </c>
       <c r="G42" s="22" t="n">
         <f aca="false">Val!E57</f>
-        <v>108.669673920527</v>
+        <v>100.722702232526</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>908</v>
